--- a/Models/КРС/results/КРС - Результаты прогнозов SARIMA.xlsx
+++ b/Models/КРС/results/КРС - Результаты прогнозов SARIMA.xlsx
@@ -488,17 +488,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>(0, 1, 2)</t>
+          <t>(3, 0, 3)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -507,22 +507,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>98.14</v>
+        <v>289.77</v>
       </c>
       <c r="G2" t="n">
-        <v>78.86</v>
+        <v>274.47</v>
       </c>
       <c r="H2" t="n">
-        <v>2.09</v>
+        <v>10.7</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>[3893.47, 3352.97, 3778.1]</t>
+          <t>[2014.14, 2734.59, 2358.48]</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>[4035.37, 3446.55, 3779.21]</t>
+          <t>[2412.7, 2909.66, 2608.27]</t>
         </is>
       </c>
     </row>
@@ -534,17 +534,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>(0, 1, 2)</t>
+          <t>(1, 0, 2)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -553,22 +553,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>86.67</v>
+        <v>153.47</v>
       </c>
       <c r="G3" t="n">
-        <v>72.95999999999999</v>
+        <v>111.22</v>
       </c>
       <c r="H3" t="n">
-        <v>1.96</v>
+        <v>3.88</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>[3454.4, 3894.89, 3595.7]</t>
+          <t>[3167.53, 2545.04, 3636.62]</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>[3446.55, 3779.21, 3691.05]</t>
+          <t>[2909.66, 2608.27, 3649.19]</t>
         </is>
       </c>
     </row>
@@ -580,17 +580,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>(0, 1, 2)</t>
+          <t>(1, 0, 2)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -599,22 +599,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>85.89</v>
+        <v>109.09</v>
       </c>
       <c r="G4" t="n">
-        <v>75.91</v>
+        <v>86.37</v>
       </c>
       <c r="H4" t="n">
-        <v>2.04</v>
+        <v>2.97</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>[3890.09, 3593.82, 3594.47]</t>
+          <t>[2443.09, 3557.47, 4255.77]</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>[3779.21, 3691.05, 3574.86]</t>
+          <t>[2608.27, 3649.19, 4253.58]</t>
         </is>
       </c>
     </row>
@@ -626,41 +626,41 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>(0, 1, 2)</t>
+          <t>(1, 0, 2)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>(2, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>188.55</v>
+        <v>243.82</v>
       </c>
       <c r="G5" t="n">
-        <v>186.77</v>
+        <v>146.11</v>
       </c>
       <c r="H5" t="n">
-        <v>4.98</v>
+        <v>3.7</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>[3496.1, 3423.01, 3737.89]</t>
+          <t>[3653.92, 4265.06, 4370.11]</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>[3691.05, 3574.86, 3951.41]</t>
+          <t>[3649.19, 4253.58, 3947.99]</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>(0, 1, 2)</t>
+          <t>(1, 0, 2)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -691,22 +691,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>87.86</v>
+        <v>254.87</v>
       </c>
       <c r="G6" t="n">
-        <v>79.09999999999999</v>
+        <v>186.87</v>
       </c>
       <c r="H6" t="n">
-        <v>3.07</v>
+        <v>4.83</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>[3656.87, 3920.52, 1905.06]</t>
+          <t>[4264.81, 4370.73, 3715.55]</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>[3574.86, 3951.41, 2029.47]</t>
+          <t>[4253.58, 3947.99, 3588.93]</t>
         </is>
       </c>
     </row>
@@ -718,17 +718,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>(0, 1, 2)</t>
+          <t>(1, 0, 2)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -737,22 +737,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>302.61</v>
+        <v>261.78</v>
       </c>
       <c r="G7" t="n">
-        <v>239.43</v>
+        <v>222.63</v>
       </c>
       <c r="H7" t="n">
-        <v>9.84</v>
+        <v>5.65</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>[3869.68, 1892.08, 1913.54]</t>
+          <t>[4365.37, 3713.27, 4189.36]</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>[3951.41, 2029.47, 2412.7]</t>
+          <t>[3947.99, 3588.93, 4315.53]</t>
         </is>
       </c>
     </row>
@@ -764,17 +764,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>(0, 1, 2)</t>
+          <t>(1, 0, 2)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -783,22 +783,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>306.87</v>
+        <v>177.48</v>
       </c>
       <c r="G8" t="n">
-        <v>260.87</v>
+        <v>155.96</v>
       </c>
       <c r="H8" t="n">
-        <v>10.69</v>
+        <v>3.82</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>[1913.71, 1926.37, 2729.13]</t>
+          <t>[3520.5, 4044.97, 3805.2]</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>[2029.47, 2412.7, 2909.66]</t>
+          <t>[3588.93, 4315.53, 3934.11]</t>
         </is>
       </c>
     </row>
@@ -810,17 +810,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>(3, 0, 3)</t>
+          <t>(1, 0, 2)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -829,22 +829,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>289.77</v>
+        <v>146.22</v>
       </c>
       <c r="G9" t="n">
-        <v>274.47</v>
+        <v>116.78</v>
       </c>
       <c r="H9" t="n">
-        <v>10.7</v>
+        <v>2.8</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>[2014.14, 2734.59, 2358.48]</t>
+          <t>[4085.83, 3828.51, 3782.02]</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>[2412.7, 2909.66, 2608.27]</t>
+          <t>[4315.53, 3934.11, 3766.97]</t>
         </is>
       </c>
     </row>
@@ -856,12 +856,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -875,22 +875,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>153.47</v>
+        <v>92.69</v>
       </c>
       <c r="G10" t="n">
-        <v>111.22</v>
+        <v>74.11</v>
       </c>
       <c r="H10" t="n">
-        <v>3.88</v>
+        <v>1.81</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>[3167.53, 2545.04, 3636.62]</t>
+          <t>[3935.06, 3852.48, 4210.65]</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>[2909.66, 2608.27, 3649.19]</t>
+          <t>[3934.11, 3766.97, 4346.53]</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -921,22 +921,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>109.09</v>
+        <v>222.24</v>
       </c>
       <c r="G11" t="n">
-        <v>86.37</v>
+        <v>190.47</v>
       </c>
       <c r="H11" t="n">
-        <v>2.97</v>
+        <v>6.57</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>[2443.09, 3557.47, 4255.77]</t>
+          <t>[3853.11, 4211.13, 2096.73]</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>[2608.27, 3649.19, 4253.58]</t>
+          <t>[3766.97, 4346.53, 2446.61]</t>
         </is>
       </c>
     </row>
@@ -948,12 +948,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -963,26 +963,26 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1217.38</v>
+        <v>777.99</v>
       </c>
       <c r="G12" t="n">
-        <v>1163.27</v>
+        <v>547.1799999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>21.84</v>
+        <v>10.95</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>[3377.86, 3892.7, 4969.95]</t>
+          <t>[4131.15, 6516.29, 3846.64]</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>[4438.18, 4677.05, 6615.11]</t>
+          <t>[4406.21, 5198.02, 3894.84]</t>
         </is>
       </c>
     </row>
@@ -994,12 +994,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1009,26 +1009,26 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>808.64</v>
+        <v>897.9299999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>722.77</v>
+        <v>624.5599999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>12.06</v>
+        <v>12.5</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>[4458.0, 5723.8, 4816.33]</t>
+          <t>[6728.68, 3973.95, 4653.66]</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>[4677.05, 6615.11, 5874.29]</t>
+          <t>[5198.02, 3894.84, 4389.74]</t>
         </is>
       </c>
     </row>
@@ -1040,12 +1040,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1055,26 +1055,26 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>810.1799999999999</v>
+        <v>619.47</v>
       </c>
       <c r="G14" t="n">
-        <v>804.89</v>
+        <v>539.36</v>
       </c>
       <c r="H14" t="n">
-        <v>13.52</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>[5869.44, 4938.88, 4751.71]</t>
+          <t>[3504.08, 4126.36, 9640.05]</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>[6615.11, 5874.29, 5485.3]</t>
+          <t>[3894.84, 4389.74, 10603.99]</t>
         </is>
       </c>
     </row>
@@ -1086,12 +1086,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1101,26 +1101,26 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>871.16</v>
+        <v>376.65</v>
       </c>
       <c r="G15" t="n">
-        <v>781.76</v>
+        <v>321.05</v>
       </c>
       <c r="H15" t="n">
-        <v>12.07</v>
+        <v>5.26</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>[5264.94, 5063.86, 8560.94]</t>
+          <t>[4346.93, 10155.49, 3994.41]</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>[5874.29, 5485.3, 7246.46]</t>
+          <t>[4389.74, 10603.99, 4466.24]</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1147,26 +1147,26 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1078.24</v>
+        <v>376.82</v>
       </c>
       <c r="G16" t="n">
-        <v>711.87</v>
+        <v>366.36</v>
       </c>
       <c r="H16" t="n">
-        <v>10.72</v>
+        <v>6.44</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>[5381.58, 9102.88, 3608.86]</t>
+          <t>[10204.62, 4012.24, 4302.51]</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>[5485.3, 7246.46, 3784.33]</t>
+          <t>[10603.99, 4466.24, 4548.23]</t>
         </is>
       </c>
     </row>
@@ -1178,12 +1178,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1193,26 +1193,26 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1133.22</v>
+        <v>395.92</v>
       </c>
       <c r="G17" t="n">
-        <v>738.4</v>
+        <v>364.99</v>
       </c>
       <c r="H17" t="n">
-        <v>11.13</v>
+        <v>6.85</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>[9200.53, 3647.87, 4281.55]</t>
+          <t>[4083.43, 4379.41, 6031.07]</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>[7246.46, 3784.33, 4406.21]</t>
+          <t>[4466.24, 4548.23, 6574.41]</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1243,22 +1243,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>665.45</v>
+        <v>208.08</v>
       </c>
       <c r="G18" t="n">
-        <v>652.34</v>
+        <v>178.24</v>
       </c>
       <c r="H18" t="n">
-        <v>14.51</v>
+        <v>2.94</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>[3250.62, 3818.47, 6033.59]</t>
+          <t>[4575.2, 6309.16, 5523.8]</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>[3784.33, 4406.21, 5198.02]</t>
+          <t>[4548.23, 6574.41, 5766.31]</t>
         </is>
       </c>
     </row>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1289,22 +1289,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>777.99</v>
+        <v>263.92</v>
       </c>
       <c r="G19" t="n">
-        <v>547.1799999999999</v>
+        <v>263.5</v>
       </c>
       <c r="H19" t="n">
-        <v>10.95</v>
+        <v>4.45</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>[4131.15, 6516.29, 3846.64]</t>
+          <t>[6290.75, 5507.51, 5198.2]</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>[4406.21, 5198.02, 3894.84]</t>
+          <t>[6574.41, 5766.31, 5446.24]</t>
         </is>
       </c>
     </row>
@@ -1316,12 +1316,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1335,22 +1335,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>897.9299999999999</v>
+        <v>227.62</v>
       </c>
       <c r="G20" t="n">
-        <v>624.5599999999999</v>
+        <v>205.7</v>
       </c>
       <c r="H20" t="n">
-        <v>12.5</v>
+        <v>3.24</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>[6728.68, 3973.95, 4653.66]</t>
+          <t>[5628.18, 5310.76, 7453.36]</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>[5198.02, 3894.84, 4389.74]</t>
+          <t>[5766.31, 5446.24, 7109.86]</t>
         </is>
       </c>
     </row>
@@ -1362,12 +1362,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1381,22 +1381,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>619.47</v>
+        <v>260.77</v>
       </c>
       <c r="G21" t="n">
-        <v>539.36</v>
+        <v>209.11</v>
       </c>
       <c r="H21" t="n">
-        <v>8.369999999999999</v>
+        <v>3.64</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>[3504.08, 4126.36, 9640.05]</t>
+          <t>[5373.12, 7537.12, 3682.38]</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>[3894.84, 4389.74, 10603.99]</t>
+          <t>[5446.24, 7109.86, 3555.44]</t>
         </is>
       </c>
     </row>
@@ -1408,41 +1408,41 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>(1, 1, 0)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1708.69</v>
+        <v>922.33</v>
       </c>
       <c r="G22" t="n">
-        <v>1389.32</v>
+        <v>658.49</v>
       </c>
       <c r="H22" t="n">
-        <v>26.79</v>
+        <v>6.26</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>[2537.16, 1726.48, 6480.29]</t>
+          <t>[5341.03, 10139.89, 8582.44]</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>[2868.77, 2841.48, 9201.63]</t>
+          <t>[5453.39, 11705.42, 8880.02]</t>
         </is>
       </c>
     </row>
@@ -1454,41 +1454,41 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>(1, 1, 0)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1350.02</v>
+        <v>829.15</v>
       </c>
       <c r="G23" t="n">
-        <v>1158.97</v>
+        <v>538.9299999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>23.76</v>
+        <v>4.8</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>[1862.76, 7119.07, 2509.22]</t>
+          <t>[10280.68, 8699.88, 5894.69]</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>[2841.48, 9201.63, 2924.85]</t>
+          <t>[11705.42, 8880.02, 5882.78]</t>
         </is>
       </c>
     </row>
@@ -1500,41 +1500,41 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>(1, 1, 0)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>378.2</v>
+        <v>537.63</v>
       </c>
       <c r="G24" t="n">
-        <v>349.44</v>
+        <v>534.47</v>
       </c>
       <c r="H24" t="n">
-        <v>9</v>
+        <v>6.56</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>[9417.46, 3475.27, 5112.81]</t>
+          <t>[9482.52, 6423.28, 11939.94]</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>[9201.63, 2924.85, 4830.75]</t>
+          <t>[8880.02, 5882.78, 12400.36]</t>
         </is>
       </c>
     </row>
@@ -1546,41 +1546,41 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>(1, 1, 0)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>331.85</v>
+        <v>583.9400000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>298.58</v>
+        <v>413.26</v>
       </c>
       <c r="H25" t="n">
-        <v>7.57</v>
+        <v>4.13</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>[3428.25, 5027.56, 13490.59]</t>
+          <t>[6141.4, 11422.57, 2988.96]</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>[2924.85, 4830.75, 13686.13]</t>
+          <t>[5882.78, 12400.36, 2992.34]</t>
         </is>
       </c>
     </row>
@@ -1592,12 +1592,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1607,26 +1607,26 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1130.12</v>
+        <v>759.77</v>
       </c>
       <c r="G26" t="n">
-        <v>848.6</v>
+        <v>531.3200000000001</v>
       </c>
       <c r="H26" t="n">
-        <v>11.65</v>
+        <v>6.95</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>[4518.35, 11782.07, 1932.56]</t>
+          <t>[11104.64, 2908.01, 2610.77]</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>[4830.75, 13686.13, 2261.91]</t>
+          <t>[12400.36, 2992.34, 2824.69]</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1653,26 +1653,26 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>889.16</v>
+        <v>469.17</v>
       </c>
       <c r="G27" t="n">
-        <v>763.5599999999999</v>
+        <v>317.23</v>
       </c>
       <c r="H27" t="n">
-        <v>11.1</v>
+        <v>4.77</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>[12335.74, 2022.17, 4752.85]</t>
+          <t>[3127.57, 2809.37, 9461.6]</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>[13686.13, 2261.91, 5453.39]</t>
+          <t>[2992.34, 2824.69, 8660.45]</t>
         </is>
       </c>
     </row>
@@ -1684,12 +1684,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1703,22 +1703,22 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1110.29</v>
+        <v>307.52</v>
       </c>
       <c r="G28" t="n">
-        <v>765.5599999999999</v>
+        <v>215.39</v>
       </c>
       <c r="H28" t="n">
-        <v>8.789999999999999</v>
+        <v>3.46</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>[2151.69, 5165.06, 9807.28]</t>
+          <t>[2724.47, 9183.05, 2998.96]</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>[2261.91, 5453.39, 11705.42]</t>
+          <t>[2824.69, 8660.45, 2975.6]</t>
         </is>
       </c>
     </row>
@@ -1730,12 +1730,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1749,22 +1749,22 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>922.33</v>
+        <v>434.75</v>
       </c>
       <c r="G29" t="n">
-        <v>658.49</v>
+        <v>317.84</v>
       </c>
       <c r="H29" t="n">
-        <v>6.26</v>
+        <v>4.73</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>[5341.03, 10139.89, 8582.44]</t>
+          <t>[9397.32, 3067.09, 4948.58]</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>[5453.39, 11705.42, 8880.02]</t>
+          <t>[8660.45, 2975.6, 4823.44]</t>
         </is>
       </c>
     </row>
@@ -1776,12 +1776,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1795,22 +1795,22 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>829.15</v>
+        <v>819.9400000000001</v>
       </c>
       <c r="G30" t="n">
-        <v>538.9299999999999</v>
+        <v>537.86</v>
       </c>
       <c r="H30" t="n">
-        <v>4.8</v>
+        <v>4.91</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>[10280.68, 8699.88, 5894.69]</t>
+          <t>[2906.63, 4691.16, 13189.2]</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>[11705.42, 8880.02, 5882.78]</t>
+          <t>[2975.6, 4823.44, 14601.52]</t>
         </is>
       </c>
     </row>
@@ -1822,12 +1822,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1841,22 +1841,22 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>537.63</v>
+        <v>787.35</v>
       </c>
       <c r="G31" t="n">
-        <v>534.47</v>
+        <v>631.53</v>
       </c>
       <c r="H31" t="n">
-        <v>6.56</v>
+        <v>10.54</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>[9482.52, 6423.28, 11939.94]</t>
+          <t>[4763.17, 13389.62, 2196.85]</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>[8880.02, 5882.78, 12400.36]</t>
+          <t>[4823.44, 14601.52, 2819.28]</t>
         </is>
       </c>
     </row>
@@ -1868,17 +1868,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>(1, 1, 0)</t>
+          <t>(2, 0, 0)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1887,22 +1887,22 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>371.48</v>
+        <v>112.64</v>
       </c>
       <c r="G32" t="n">
-        <v>343.67</v>
+        <v>99.91</v>
       </c>
       <c r="H32" t="n">
-        <v>21.68</v>
+        <v>4.75</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>[1145.03, 1210.75, 1231.19]</t>
+          <t>[1610.16, 2162.92, 1889.23]</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>[1377.01, 1753.35, 1487.62]</t>
+          <t>[1640.07, 2317.39, 2004.6]</t>
         </is>
       </c>
     </row>
@@ -1914,17 +1914,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>(1, 1, 0)</t>
+          <t>(2, 0, 0)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1933,22 +1933,22 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>282.88</v>
+        <v>102.6</v>
       </c>
       <c r="G33" t="n">
-        <v>241.76</v>
+        <v>98</v>
       </c>
       <c r="H33" t="n">
-        <v>16.2</v>
+        <v>4.2</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>[1364.84, 1446.54, 952.62]</t>
+          <t>[2180.06, 1911.37, 3187.61]</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>[1753.35, 1487.62, 1248.3]</t>
+          <t>[2317.39, 2004.6, 3124.16]</t>
         </is>
       </c>
     </row>
@@ -1960,17 +1960,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>(1, 1, 0)</t>
+          <t>(2, 0, 0)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1979,22 +1979,22 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>145.51</v>
+        <v>129.97</v>
       </c>
       <c r="G34" t="n">
-        <v>140.74</v>
+        <v>115.84</v>
       </c>
       <c r="H34" t="n">
-        <v>9.74</v>
+        <v>3.79</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>[1671.31, 1154.84, 1689.77]</t>
+          <t>[1962.36, 3310.66, 3476.04]</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>[1487.62, 1248.3, 1544.7]</t>
+          <t>[2004.6, 3124.16, 3594.82]</t>
         </is>
       </c>
     </row>
@@ -2006,17 +2006,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>(1, 1, 0)</t>
+          <t>(2, 0, 0)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2025,22 +2025,22 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>94.7</v>
+        <v>162.45</v>
       </c>
       <c r="G35" t="n">
-        <v>64.69</v>
+        <v>150.68</v>
       </c>
       <c r="H35" t="n">
-        <v>5.01</v>
+        <v>6.41</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>[1086.93, 1548.18, 1530.08]</t>
+          <t>[3342.42, 3523.75, 1421.14]</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>[1248.3, 1544.7, 1559.28]</t>
+          <t>[3124.16, 3594.82, 1583.87]</t>
         </is>
       </c>
     </row>
@@ -2052,12 +2052,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2071,22 +2071,22 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>117.54</v>
+        <v>290.22</v>
       </c>
       <c r="G36" t="n">
-        <v>100.23</v>
+        <v>270.56</v>
       </c>
       <c r="H36" t="n">
-        <v>6.66</v>
+        <v>13.11</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>[1673.94, 1715.88, 925.89]</t>
+          <t>[3418.75, 1365.26, 1603.85]</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>[1544.7, 1559.28, 940.75]</t>
+          <t>[3594.82, 1583.87, 2020.86]</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2117,22 +2117,22 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>72.23999999999999</v>
+        <v>278.32</v>
       </c>
       <c r="G37" t="n">
-        <v>65.40000000000001</v>
+        <v>267.99</v>
       </c>
       <c r="H37" t="n">
-        <v>5.03</v>
+        <v>14.78</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>[1664.02, 879.18, 1610.17]</t>
+          <t>[1393.29, 1651.17, 1496.52]</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>[1559.28, 940.75, 1640.07]</t>
+          <t>[1583.87, 2020.86, 1740.22]</t>
         </is>
       </c>
     </row>
@@ -2144,12 +2144,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2159,26 +2159,26 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>179.83</v>
+        <v>144.25</v>
       </c>
       <c r="G38" t="n">
-        <v>155.05</v>
+        <v>127.95</v>
       </c>
       <c r="H38" t="n">
-        <v>9.050000000000001</v>
+        <v>7.48</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>[855.86, 1543.49, 2033.7]</t>
+          <t>[1827.68, 1703.76, 1274.87]</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>[940.75, 1640.07, 2317.39]</t>
+          <t>[2020.86, 1740.22, 1429.08]</t>
         </is>
       </c>
     </row>
@@ -2190,12 +2190,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2205,26 +2205,26 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>112.64</v>
+        <v>73.27</v>
       </c>
       <c r="G39" t="n">
-        <v>99.91</v>
+        <v>67.08</v>
       </c>
       <c r="H39" t="n">
-        <v>4.75</v>
+        <v>4.22</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>[1610.16, 2162.92, 1889.23]</t>
+          <t>[1769.07, 1357.33, 1786.98]</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>[1640.07, 2317.39, 2004.6]</t>
+          <t>[1740.22, 1429.08, 1686.36]</t>
         </is>
       </c>
     </row>
@@ -2236,12 +2236,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2251,26 +2251,26 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>102.6</v>
+        <v>67.36</v>
       </c>
       <c r="G40" t="n">
-        <v>98</v>
+        <v>60.86</v>
       </c>
       <c r="H40" t="n">
-        <v>4.2</v>
+        <v>3.88</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>[2180.06, 1911.37, 3187.61]</t>
+          <t>[1348.11, 1767.95, 1745.09]</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>[2317.39, 2004.6, 3124.16]</t>
+          <t>[1429.08, 1686.36, 1765.1]</t>
         </is>
       </c>
     </row>
@@ -2282,12 +2282,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2297,26 +2297,26 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>129.97</v>
+        <v>77.81</v>
       </c>
       <c r="G41" t="n">
-        <v>115.84</v>
+        <v>63.15</v>
       </c>
       <c r="H41" t="n">
-        <v>3.79</v>
+        <v>3.96</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>[1962.36, 3310.66, 3476.04]</t>
+          <t>[1812.03, 1809.94, 1026.04]</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>[2004.6, 3124.16, 3594.82]</t>
+          <t>[1686.36, 1765.1, 1007.1]</t>
         </is>
       </c>
     </row>
@@ -2328,12 +2328,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2347,22 +2347,22 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>455.98</v>
+        <v>113.93</v>
       </c>
       <c r="G42" t="n">
-        <v>446.73</v>
+        <v>87.56</v>
       </c>
       <c r="H42" t="n">
-        <v>19.24</v>
+        <v>2.66</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>[1382.94, 2111.61, 2352.13]</t>
+          <t>[2781.03, 4988.64, 3210.04]</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>[1822.26, 2673.77, 2690.83]</t>
+          <t>[2845.28, 5000.88, 3396.22]</t>
         </is>
       </c>
     </row>
@@ -2374,12 +2374,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2393,22 +2393,22 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>303.39</v>
+        <v>105.88</v>
       </c>
       <c r="G43" t="n">
-        <v>276.19</v>
+        <v>105.77</v>
       </c>
       <c r="H43" t="n">
-        <v>11.19</v>
+        <v>2.53</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>[2777.31, 3089.22, 2520.82]</t>
+          <t>[5103.67, 3283.92, 4681.04]</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>[2673.77, 2690.83, 2194.18]</t>
+          <t>[5000.88, 3396.22, 4578.81]</t>
         </is>
       </c>
     </row>
@@ -2420,12 +2420,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2439,22 +2439,22 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>266.69</v>
+        <v>148.97</v>
       </c>
       <c r="G44" t="n">
-        <v>265.68</v>
+        <v>124.26</v>
       </c>
       <c r="H44" t="n">
-        <v>10.14</v>
+        <v>2.43</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>[2973.8, 2427.11, 2748.83]</t>
+          <t>[3217.65, 4586.96, 10144.47]</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>[2690.83, 2194.18, 3029.97]</t>
+          <t>[3396.22, 4578.81, 9958.4]</t>
         </is>
       </c>
     </row>
@@ -2466,12 +2466,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2485,22 +2485,22 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1027.94</v>
+        <v>480.01</v>
       </c>
       <c r="G45" t="n">
-        <v>747.33</v>
+        <v>418.68</v>
       </c>
       <c r="H45" t="n">
-        <v>15.49</v>
+        <v>9.5</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>[2196.61, 2485.57, 4276.5]</t>
+          <t>[4841.64, 10708.89, 1836.75]</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>[2194.18, 3029.97, 5971.67]</t>
+          <t>[4578.81, 9958.4, 1594.05]</t>
         </is>
       </c>
     </row>
@@ -2512,12 +2512,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2531,22 +2531,22 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1135.07</v>
+        <v>135.9</v>
       </c>
       <c r="G46" t="n">
-        <v>1024.04</v>
+        <v>130.81</v>
       </c>
       <c r="H46" t="n">
-        <v>23.17</v>
+        <v>4.55</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>[2480.51, 4273.67, 2768.73]</t>
+          <t>[10127.04, 1736.97, 2624.05]</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>[3029.97, 5971.67, 3593.38]</t>
+          <t>[9958.4, 1594.05, 2704.93]</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2577,22 +2577,22 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>561.23</v>
+        <v>97.56999999999999</v>
       </c>
       <c r="G47" t="n">
-        <v>500.69</v>
+        <v>81.56999999999999</v>
       </c>
       <c r="H47" t="n">
-        <v>11.54</v>
+        <v>3.99</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>[5112.43, 3268.89, 2526.96]</t>
+          <t>[1708.06, 2580.34, 2803.82]</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>[5971.67, 3593.38, 2845.28]</t>
+          <t>[1594.05, 2704.93, 2809.92]</t>
         </is>
       </c>
     </row>
@@ -2604,12 +2604,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2623,22 +2623,22 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>272.87</v>
+        <v>208.21</v>
       </c>
       <c r="G48" t="n">
-        <v>258.03</v>
+        <v>186.44</v>
       </c>
       <c r="H48" t="n">
-        <v>6.59</v>
+        <v>7</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>[3861.78, 2989.81, 5362.05]</t>
+          <t>[2408.23, 2617.22, 2134.84]</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>[3593.38, 2845.28, 5000.88]</t>
+          <t>[2704.93, 2809.92, 2204.76]</t>
         </is>
       </c>
     </row>
@@ -2650,12 +2650,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2669,22 +2669,22 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>113.93</v>
+        <v>134.99</v>
       </c>
       <c r="G49" t="n">
-        <v>87.56</v>
+        <v>111.23</v>
       </c>
       <c r="H49" t="n">
-        <v>2.66</v>
+        <v>4.59</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>[2781.03, 4988.64, 3210.04]</t>
+          <t>[2940.27, 2398.63, 2846.65]</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>[2845.28, 5000.88, 3396.22]</t>
+          <t>[2809.92, 2204.76, 2856.12]</t>
         </is>
       </c>
     </row>
@@ -2696,12 +2696,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2715,22 +2715,22 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>105.88</v>
+        <v>772.95</v>
       </c>
       <c r="G50" t="n">
-        <v>105.77</v>
+        <v>516.9400000000001</v>
       </c>
       <c r="H50" t="n">
-        <v>2.53</v>
+        <v>10.1</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>[5103.67, 3283.92, 4681.04]</t>
+          <t>[2292.14, 2721.86, 4818.29]</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>[5000.88, 3396.22, 4578.81]</t>
+          <t>[2204.76, 2856.12, 6147.46]</t>
         </is>
       </c>
     </row>
@@ -2742,12 +2742,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2761,22 +2761,22 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>148.97</v>
+        <v>992.39</v>
       </c>
       <c r="G51" t="n">
-        <v>124.26</v>
+        <v>843.77</v>
       </c>
       <c r="H51" t="n">
-        <v>2.43</v>
+        <v>17.97</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>[3217.65, 4586.96, 10144.47]</t>
+          <t>[2617.94, 4634.43, 2943.83]</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>[3396.22, 4578.81, 9958.4]</t>
+          <t>[2856.12, 6147.46, 3723.94]</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2803,26 +2803,26 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>3.24</v>
+        <v>6.84</v>
       </c>
       <c r="G52" t="n">
-        <v>2.73</v>
+        <v>5.29</v>
       </c>
       <c r="H52" t="n">
-        <v>99.87</v>
+        <v>81.55</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.01]</t>
+          <t>[0.0, 1.07, 1.87]</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>[0.3, 4.3, 3.6]</t>
+          <t>[2.3, 12.5, 4.0]</t>
         </is>
       </c>
     </row>
@@ -2834,12 +2834,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2853,22 +2853,22 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>3.73</v>
+        <v>7.19</v>
       </c>
       <c r="G53" t="n">
-        <v>3.7</v>
+        <v>6.06</v>
       </c>
       <c r="H53" t="n">
-        <v>96.45999999999999</v>
+        <v>75.38</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>[0.02, 0.0, 0.37]</t>
+          <t>[1.02, 1.4, 1.81]</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>[4.3, 3.6, 3.6]</t>
+          <t>[12.5, 4.0, 5.9]</t>
         </is>
       </c>
     </row>
@@ -2880,12 +2880,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2899,22 +2899,22 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>3.16</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="G54" t="n">
-        <v>3.13</v>
+        <v>6.76</v>
       </c>
       <c r="H54" t="n">
-        <v>96.29000000000001</v>
+        <v>68.01000000000001</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>[0.0, 0.4, 0.0]</t>
+          <t>[1.48, 1.89, 5.06]</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>[3.6, 3.6, 2.6]</t>
+          <t>[4.0, 5.9, 18.8]</t>
         </is>
       </c>
     </row>
@@ -2926,17 +2926,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>(1, 0, 0)</t>
+          <t>(0, 0, 0)</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2945,22 +2945,22 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>2.22</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="G55" t="n">
-        <v>2.18</v>
+        <v>6.61</v>
       </c>
       <c r="H55" t="n">
-        <v>78.09999999999999</v>
+        <v>78.69</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>[1.27, 0.0, 0.7]</t>
+          <t>[1.92, 5.17, 0.09]</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>[3.6, 2.6, 2.3]</t>
+          <t>[5.9, 18.8, 2.3]</t>
         </is>
       </c>
     </row>
@@ -2972,17 +2972,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>(1, 0, 0)</t>
+          <t>(0, 0, 0)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2991,22 +2991,22 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1.76</v>
+        <v>8.06</v>
       </c>
       <c r="G56" t="n">
-        <v>1.5</v>
+        <v>6.08</v>
       </c>
       <c r="H56" t="n">
-        <v>94.75</v>
+        <v>87.67</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>[0.0, 0.73, 0.65]</t>
+          <t>[5.25, 0.09, 0.13]</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>[2.6, 2.3, 0.3]</t>
+          <t>[18.8, 2.3, 2.6]</t>
         </is>
       </c>
     </row>
@@ -3018,17 +3018,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>(1, 0, 0)</t>
+          <t>(0, 0, 0)</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3037,22 +3037,22 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1.35</v>
+        <v>1.91</v>
       </c>
       <c r="G57" t="n">
-        <v>0.9</v>
+        <v>1.62</v>
       </c>
       <c r="H57" t="n">
-        <v>76.77</v>
+        <v>85.27</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>[2.32, 0.69, 0.0]</t>
+          <t>[0.09, 0.14, 0.1]</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>[2.3, 0.3, 2.3]</t>
+          <t>[2.3, 2.6, 0.3]</t>
         </is>
       </c>
     </row>
@@ -3064,17 +3064,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>(1, 0, 0)</t>
+          <t>(0, 0, 0)</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3083,22 +3083,22 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>6.71</v>
+        <v>1.5</v>
       </c>
       <c r="G58" t="n">
-        <v>4.69</v>
+        <v>1.15</v>
       </c>
       <c r="H58" t="n">
-        <v>106.45</v>
+        <v>6.389490467893594e+22</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>[0.68, 0.0, 1.11]</t>
+          <t>[0.14, 0.11, 0.81]</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>[0.3, 2.3, 12.5]</t>
+          <t>[2.6, 0.3, 0.0]</t>
         </is>
       </c>
     </row>
@@ -3110,12 +3110,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3129,22 +3129,22 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>6.84</v>
+        <v>0.55</v>
       </c>
       <c r="G59" t="n">
-        <v>5.29</v>
+        <v>0.38</v>
       </c>
       <c r="H59" t="n">
-        <v>81.55</v>
+        <v>7.697875867699967e+22</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>[0.0, 1.07, 1.87]</t>
+          <t>[0.15, 0.94, 0.04]</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>[2.3, 12.5, 4.0]</t>
+          <t>[0.3, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -3156,17 +3156,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3175,22 +3175,22 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>7.19</v>
+        <v>25.73</v>
       </c>
       <c r="G60" t="n">
-        <v>6.06</v>
+        <v>15.21</v>
       </c>
       <c r="H60" t="n">
-        <v>75.38</v>
+        <v>8.501762777128306e+22</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>[1.02, 1.4, 1.81]</t>
+          <t>[1.04, 0.04, 0.94]</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>[12.5, 4.0, 5.9]</t>
+          <t>[0.0, 0.0, 45.5]</t>
         </is>
       </c>
     </row>
@@ -3202,12 +3202,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3221,22 +3221,22 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>8.390000000000001</v>
+        <v>36</v>
       </c>
       <c r="G61" t="n">
-        <v>6.76</v>
+        <v>29.4</v>
       </c>
       <c r="H61" t="n">
-        <v>68.01000000000001</v>
+        <v>2.715365127116205e+21</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>[1.48, 1.89, 5.06]</t>
+          <t>[0.03, 0.72, 0.2]</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>[4.0, 5.9, 18.8]</t>
+          <t>[0.0, 45.5, 43.6]</t>
         </is>
       </c>
     </row>
@@ -3248,12 +3248,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3267,22 +3267,22 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>1.27</v>
+        <v>0.38</v>
       </c>
       <c r="G62" t="n">
-        <v>1.01</v>
+        <v>0.32</v>
       </c>
       <c r="H62" t="n">
-        <v>29.24</v>
+        <v>15.69</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>[2.14, 4.56, 5.42]</t>
+          <t>[1.19, 3.37, 3.02]</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>[2.2, 3.5, 3.5]</t>
+          <t>[1.7, 3.4, 2.6]</t>
         </is>
       </c>
     </row>
@@ -3294,12 +3294,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3313,22 +3313,22 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>1.66</v>
+        <v>0.66</v>
       </c>
       <c r="G63" t="n">
-        <v>1.62</v>
+        <v>0.6</v>
       </c>
       <c r="H63" t="n">
-        <v>51.2</v>
+        <v>22.21</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>[4.61, 5.48, 4.46]</t>
+          <t>[4.01, 3.53, 2.26]</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>[3.5, 3.5, 2.7]</t>
+          <t>[3.4, 2.6, 2.0]</t>
         </is>
       </c>
     </row>
@@ -3340,12 +3340,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3359,22 +3359,22 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1.14</v>
+        <v>0.5</v>
       </c>
       <c r="G64" t="n">
-        <v>1.09</v>
+        <v>0.44</v>
       </c>
       <c r="H64" t="n">
-        <v>38.71</v>
+        <v>15.41</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>[4.84, 4.01, 2.72]</t>
+          <t>[3.28, 2.11, 4.13]</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>[3.5, 2.7, 2.1]</t>
+          <t>[2.6, 2.0, 3.6]</t>
         </is>
       </c>
     </row>
@@ -3386,12 +3386,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3405,22 +3405,22 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>0.63</v>
+        <v>0.11</v>
       </c>
       <c r="G65" t="n">
-        <v>0.59</v>
+        <v>0.11</v>
       </c>
       <c r="H65" t="n">
-        <v>22.9</v>
+        <v>4.53</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>[3.45, 2.39, 3.43]</t>
+          <t>[1.89, 3.74, 1.63]</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>[2.7, 2.1, 2.7]</t>
+          <t>[2.0, 3.6, 1.7]</t>
         </is>
       </c>
     </row>
@@ -3432,41 +3432,41 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>(2, 0, 0)</t>
+          <t>(2, 0, 2)</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(1, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="G66" t="n">
-        <v>0.43</v>
+        <v>0.08</v>
       </c>
       <c r="H66" t="n">
-        <v>22.61</v>
+        <v>2.89</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>[2.12, 3.09, 2.59]</t>
+          <t>[3.54, 1.68, 2.85]</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>[2.1, 2.7, 1.7]</t>
+          <t>[3.6, 1.7, 2.7]</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3497,22 +3497,22 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="G67" t="n">
-        <v>0.49</v>
+        <v>0.05</v>
       </c>
       <c r="H67" t="n">
-        <v>25.82</v>
+        <v>2.53</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>[3.08, 2.58, 1.5]</t>
+          <t>[1.62, 2.64, 2.72]</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>[2.7, 1.7, 1.7]</t>
+          <t>[1.7, 2.7, 2.7]</t>
         </is>
       </c>
     </row>
@@ -3524,12 +3524,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3543,22 +3543,22 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>0.55</v>
+        <v>0.1</v>
       </c>
       <c r="G68" t="n">
-        <v>0.52</v>
+        <v>0.08</v>
       </c>
       <c r="H68" t="n">
-        <v>24.98</v>
+        <v>3.67</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>[2.42, 1.42, 3.95]</t>
+          <t>[2.7, 2.77, 2.16]</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>[1.7, 1.7, 3.4]</t>
+          <t>[2.7, 2.7, 2.0]</t>
         </is>
       </c>
     </row>
@@ -3570,12 +3570,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3589,22 +3589,22 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>0.38</v>
+        <v>0.25</v>
       </c>
       <c r="G69" t="n">
-        <v>0.32</v>
+        <v>0.21</v>
       </c>
       <c r="H69" t="n">
-        <v>15.69</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>[1.19, 3.37, 3.02]</t>
+          <t>[2.77, 2.16, 1.7]</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>[1.7, 3.4, 2.6]</t>
+          <t>[2.7, 2.0, 2.1]</t>
         </is>
       </c>
     </row>
@@ -3616,12 +3616,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3635,22 +3635,22 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>0.66</v>
+        <v>0.35</v>
       </c>
       <c r="G70" t="n">
-        <v>0.6</v>
+        <v>0.32</v>
       </c>
       <c r="H70" t="n">
-        <v>22.21</v>
+        <v>14.25</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>[4.01, 3.53, 2.26]</t>
+          <t>[2.14, 1.68, 2.19]</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>[3.4, 2.6, 2.0]</t>
+          <t>[2.0, 2.1, 2.6]</t>
         </is>
       </c>
     </row>
@@ -3662,12 +3662,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3681,22 +3681,22 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="G71" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="H71" t="n">
-        <v>15.41</v>
+        <v>20.22</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>[3.28, 2.11, 4.13]</t>
+          <t>[1.63, 2.12, 1.36]</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>[2.6, 2.0, 3.6]</t>
+          <t>[2.1, 2.6, 1.7]</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3727,22 +3727,22 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>40.52</v>
+        <v>614.62</v>
       </c>
       <c r="G72" t="n">
-        <v>35.95</v>
+        <v>367.58</v>
       </c>
       <c r="H72" t="n">
-        <v>6.27</v>
+        <v>79.72</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>[744.67, 571.27, 580.83]</t>
+          <t>[347.77, 383.71, 1530.46]</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>[767.55, 593.84, 518.43]</t>
+          <t>[352.82, 350.02, 466.45]</t>
         </is>
       </c>
     </row>
@@ -3754,12 +3754,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3773,22 +3773,22 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>45.36</v>
+        <v>621.59</v>
       </c>
       <c r="G73" t="n">
-        <v>39.02</v>
+        <v>394.27</v>
       </c>
       <c r="H73" t="n">
-        <v>7.39</v>
+        <v>85.09</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>[579.08, 588.57, 555.29]</t>
+          <t>[386.2, 1539.98, 420.95]</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>[593.84, 518.43, 523.12]</t>
+          <t>[350.02, 466.45, 494.05]</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3819,22 +3819,22 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>51.38</v>
+        <v>586.13</v>
       </c>
       <c r="G74" t="n">
-        <v>46.18</v>
+        <v>396.48</v>
       </c>
       <c r="H74" t="n">
-        <v>9.24</v>
+        <v>82.19</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>[595.28, 561.39, 443.72]</t>
+          <t>[1473.42, 403.42, 652.7]</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>[518.43, 523.12, 420.32]</t>
+          <t>[466.45, 494.05, 744.54]</t>
         </is>
       </c>
     </row>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3861,26 +3861,26 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>6.83</v>
+        <v>189.16</v>
       </c>
       <c r="G75" t="n">
-        <v>5.83</v>
+        <v>177.77</v>
       </c>
       <c r="H75" t="n">
-        <v>1.12</v>
+        <v>29.43</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>[527.56, 418.01, 555.96]</t>
+          <t>[270.11, 521.53, 577.24]</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>[523.12, 420.32, 545.23]</t>
+          <t>[494.05, 744.54, 663.61]</t>
         </is>
       </c>
     </row>
@@ -3892,12 +3892,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3907,26 +3907,26 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>21.36</v>
+        <v>58.01</v>
       </c>
       <c r="G76" t="n">
-        <v>16.12</v>
+        <v>54.22</v>
       </c>
       <c r="H76" t="n">
-        <v>4.01</v>
+        <v>7.98</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>[416.43, 553.94, 411.41]</t>
+          <t>[691.78, 743.79, 593.85]</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>[420.32, 545.23, 375.66]</t>
+          <t>[744.54, 663.61, 623.57]</t>
         </is>
       </c>
     </row>
@@ -3938,12 +3938,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3953,26 +3953,26 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>23.52</v>
+        <v>101.51</v>
       </c>
       <c r="G77" t="n">
-        <v>20.06</v>
+        <v>85.63</v>
       </c>
       <c r="H77" t="n">
-        <v>5.1</v>
+        <v>17.67</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>[556.25, 413.06, 364.59]</t>
+          <t>[765.11, 611.2, 543.41]</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>[545.23, 375.66, 352.82]</t>
+          <t>[663.61, 623.57, 400.39]</t>
         </is>
       </c>
     </row>
@@ -3984,12 +3984,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3999,26 +3999,26 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>34.31</v>
+        <v>115.85</v>
       </c>
       <c r="G78" t="n">
-        <v>30.17</v>
+        <v>106.98</v>
       </c>
       <c r="H78" t="n">
-        <v>8.390000000000001</v>
+        <v>25.13</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>[409.37, 361.46, 398.19]</t>
+          <t>[573.62, 512.97, 561.81]</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>[375.66, 352.82, 350.02]</t>
+          <t>[623.57, 400.39, 403.4]</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4045,26 +4045,26 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>614.62</v>
+        <v>129.8</v>
       </c>
       <c r="G79" t="n">
-        <v>367.58</v>
+        <v>115.44</v>
       </c>
       <c r="H79" t="n">
-        <v>79.72</v>
+        <v>28.48</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>[347.77, 383.71, 1530.46]</t>
+          <t>[532.53, 581.71, 471.63]</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>[352.82, 350.02, 466.45]</t>
+          <t>[400.39, 403.4, 435.75]</t>
         </is>
       </c>
     </row>
@@ -4076,12 +4076,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4091,26 +4091,26 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>621.59</v>
+        <v>69.11</v>
       </c>
       <c r="G80" t="n">
-        <v>394.27</v>
+        <v>57.25</v>
       </c>
       <c r="H80" t="n">
-        <v>85.09</v>
+        <v>13.24</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>[386.2, 1539.98, 420.95]</t>
+          <t>[512.3, 420.04, 564.84]</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>[350.02, 466.45, 494.05]</t>
+          <t>[403.4, 435.75, 517.7]</t>
         </is>
       </c>
     </row>
@@ -4122,12 +4122,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4137,26 +4137,26 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>586.13</v>
+        <v>37.61</v>
       </c>
       <c r="G81" t="n">
-        <v>396.48</v>
+        <v>30.41</v>
       </c>
       <c r="H81" t="n">
-        <v>82.19</v>
+        <v>7.12</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>[1473.42, 403.42, 652.7]</t>
+          <t>[375.05, 509.24, 357.83]</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>[466.45, 494.05, 744.54]</t>
+          <t>[435.75, 517.7, 379.9]</t>
         </is>
       </c>
     </row>
@@ -4168,41 +4168,41 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(2, 1, 2)</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>(0, 1, 2, 12)</t>
+          <t>(1, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>834.6900000000001</v>
+        <v>106.57</v>
       </c>
       <c r="G82" t="n">
-        <v>742.25</v>
+        <v>79.65000000000001</v>
       </c>
       <c r="H82" t="n">
-        <v>21.37</v>
+        <v>1.85</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>[2165.52, 2454.29, 2883.72]</t>
+          <t>[4424.8, 4437.78, 3415.78]</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>[2452.32, 3173.15, 4104.82]</t>
+          <t>[4488.08, 4264.39, 3418.05]</t>
         </is>
       </c>
     </row>
@@ -4214,41 +4214,41 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(1, 1, 2)</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>(0, 1, 2, 12)</t>
+          <t>(1, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>845.99</v>
+        <v>202.43</v>
       </c>
       <c r="G83" t="n">
-        <v>808.0599999999999</v>
+        <v>164.99</v>
       </c>
       <c r="H83" t="n">
-        <v>22.58</v>
+        <v>3.32</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>[2533.32, 2942.68, 2609.3]</t>
+          <t>[4470.74, 3423.24, 5991.92]</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>[3173.15, 4104.82, 3231.51]</t>
+          <t>[4264.39, 3418.05, 5708.5]</t>
         </is>
       </c>
     </row>
@@ -4260,41 +4260,41 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(1, 1, 2)</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>(0, 1, 2, 12)</t>
+          <t>(2, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>632.26</v>
+        <v>575.79</v>
       </c>
       <c r="G84" t="n">
-        <v>588.37</v>
+        <v>372.72</v>
       </c>
       <c r="H84" t="n">
-        <v>16.22</v>
+        <v>2.91</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>[3190.72, 2834.01, 2761.73]</t>
+          <t>[3416.48, 5835.96, 14361.65]</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>[4104.82, 3231.51, 3215.25]</t>
+          <t>[3418.05, 5708.5, 15350.76]</t>
         </is>
       </c>
     </row>
@@ -4306,12 +4306,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4321,26 +4321,26 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>(0, 1, 2, 12)</t>
+          <t>(2, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>297.35</v>
+        <v>576.99</v>
       </c>
       <c r="G85" t="n">
-        <v>289</v>
+        <v>394.49</v>
       </c>
       <c r="H85" t="n">
-        <v>8.34</v>
+        <v>3.82</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>[2843.86, 2968.55, 4584.68]</t>
+          <t>[5837.31, 14361.9, 2452.21]</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>[3231.51, 3215.25, 4352.03]</t>
+          <t>[5708.5, 15350.76, 2386.42]</t>
         </is>
       </c>
     </row>
@@ -4352,17 +4352,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>(1, 1, 2)</t>
+          <t>(1, 1, 3)</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -4371,22 +4371,22 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>241.26</v>
+        <v>810.85</v>
       </c>
       <c r="G86" t="n">
-        <v>206.64</v>
+        <v>558.66</v>
       </c>
       <c r="H86" t="n">
-        <v>5.82</v>
+        <v>6.81</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>[3112.29, 4733.78, 2326.09]</t>
+          <t>[13965.09, 2603.03, 3089.61]</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>[3215.25, 4352.03, 2461.28]</t>
+          <t>[15350.76, 2386.42, 3163.3]</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4417,22 +4417,22 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>265.71</v>
+        <v>716.5599999999999</v>
       </c>
       <c r="G87" t="n">
-        <v>210.29</v>
+        <v>498.14</v>
       </c>
       <c r="H87" t="n">
-        <v>5.49</v>
+        <v>18.83</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>[4790.89, 2345.69, 4411.66]</t>
+          <t>[2671.92, 3162.21, 3922.84]</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>[4352.03, 2461.28, 4488.08]</t>
+          <t>[2386.42, 3163.3, 2715.0]</t>
         </is>
       </c>
     </row>
@@ -4444,17 +4444,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(1, 1, 2)</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -4463,22 +4463,22 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>152.04</v>
+        <v>666.3099999999999</v>
       </c>
       <c r="G88" t="n">
-        <v>141.37</v>
+        <v>486.15</v>
       </c>
       <c r="H88" t="n">
-        <v>4.54</v>
+        <v>17.29</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>[2240.85, 4383.77, 4363.76]</t>
+          <t>[3020.01, 3845.1, 3059.98]</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>[2461.28, 4488.08, 4264.39]</t>
+          <t>[3163.3, 2715.0, 3245.04]</t>
         </is>
       </c>
     </row>
@@ -4490,41 +4490,41 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>(2, 1, 2)</t>
+          <t>(1, 1, 2)</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>(1, 1, 1, 12)</t>
+          <t>(0, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>106.57</v>
+        <v>725.24</v>
       </c>
       <c r="G89" t="n">
-        <v>79.65000000000001</v>
+        <v>562.85</v>
       </c>
       <c r="H89" t="n">
-        <v>1.85</v>
+        <v>19.54</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>[4424.8, 4437.78, 3415.78]</t>
+          <t>[3916.84, 3088.53, 3134.1]</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>[4488.08, 4264.39, 3418.05]</t>
+          <t>[2715.0, 3245.04, 3464.3]</t>
         </is>
       </c>
     </row>
@@ -4536,41 +4536,41 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>(1, 1, 2)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>(1, 1, 1, 12)</t>
+          <t>(0, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>202.43</v>
+        <v>1423.17</v>
       </c>
       <c r="G90" t="n">
-        <v>164.99</v>
+        <v>1119.83</v>
       </c>
       <c r="H90" t="n">
-        <v>3.32</v>
+        <v>22.09</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>[4470.74, 3423.24, 5991.92]</t>
+          <t>[2882.97, 2817.9, 4097.94]</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>[4264.39, 3418.05, 5708.5]</t>
+          <t>[3245.04, 3464.3, 6448.97]</t>
         </is>
       </c>
     </row>
@@ -4582,41 +4582,41 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>(1, 1, 2)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>(2, 1, 0, 12)</t>
+          <t>(0, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>575.79</v>
+        <v>1322</v>
       </c>
       <c r="G91" t="n">
-        <v>372.72</v>
+        <v>977.35</v>
       </c>
       <c r="H91" t="n">
-        <v>2.91</v>
+        <v>19.02</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>[3416.48, 5835.96, 14361.65]</t>
+          <t>[2911.12, 4233.0, 2256.69]</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>[3418.05, 5708.5, 15350.76]</t>
+          <t>[3464.3, 6448.97, 2419.61]</t>
         </is>
       </c>
     </row>
@@ -4628,41 +4628,41 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>(0, 0, 1)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(0, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>116.38</v>
+        <v>247.41</v>
       </c>
       <c r="G92" t="n">
-        <v>100.14</v>
+        <v>201.93</v>
       </c>
       <c r="H92" t="n">
-        <v>2.71</v>
+        <v>4.79</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>[2705.73, 3333.11, 4402.76]</t>
+          <t>[3486.67, 5646.43, 3625.3]</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>[2800.48, 3363.48, 4578.07]</t>
+          <t>[3873.69, 5466.61, 3586.35]</t>
         </is>
       </c>
     </row>
@@ -4674,12 +4674,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4689,26 +4689,26 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(0, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>153.27</v>
+        <v>267.15</v>
       </c>
       <c r="G93" t="n">
-        <v>126.2</v>
+        <v>193.94</v>
       </c>
       <c r="H93" t="n">
-        <v>2.98</v>
+        <v>3.73</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>[3367.44, 4402.46, 3785.3]</t>
+          <t>[5910.29, 3593.27, 4446.84]</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>[3363.48, 4578.07, 3984.34]</t>
+          <t>[5466.61, 3586.35, 4578.05]</t>
         </is>
       </c>
     </row>
@@ -4720,12 +4720,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4735,26 +4735,26 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(0, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>229.11</v>
+        <v>361.61</v>
       </c>
       <c r="G94" t="n">
-        <v>223.44</v>
+        <v>277.44</v>
       </c>
       <c r="H94" t="n">
-        <v>5.28</v>
+        <v>4.06</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>[4400.79, 3785.21, 3922.88]</t>
+          <t>[3509.48, 4425.08, 8397.91]</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>[4578.07, 3984.34, 4216.8]</t>
+          <t>[3586.35, 4578.05, 9000.38]</t>
         </is>
       </c>
     </row>
@@ -4766,12 +4766,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -4781,26 +4781,26 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(0, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>194.28</v>
+        <v>378.03</v>
       </c>
       <c r="G95" t="n">
-        <v>180.16</v>
+        <v>327.92</v>
       </c>
       <c r="H95" t="n">
-        <v>3.94</v>
+        <v>6.63</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>[3833.68, 3936.56, 8007.11]</t>
+          <t>[4448.42, 8419.78, 2855.8]</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>[3984.34, 4216.8, 7897.55]</t>
+          <t>[4578.05, 9000.38, 2582.26]</t>
         </is>
       </c>
     </row>
@@ -4812,12 +4812,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4827,26 +4827,26 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(0, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>177.74</v>
+        <v>343.57</v>
       </c>
       <c r="G96" t="n">
-        <v>171.79</v>
+        <v>297.93</v>
       </c>
       <c r="H96" t="n">
-        <v>4.09</v>
+        <v>6.43</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>[3986.51, 8016.61, 2967.11]</t>
+          <t>[8481.34, 2854.77, 3545.66]</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>[4216.8, 7897.55, 3133.14]</t>
+          <t>[9000.38, 2582.26, 3443.42]</t>
         </is>
       </c>
     </row>
@@ -4858,12 +4858,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -4877,22 +4877,22 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>332.25</v>
+        <v>234.27</v>
       </c>
       <c r="G97" t="n">
-        <v>308.82</v>
+        <v>192.07</v>
       </c>
       <c r="H97" t="n">
-        <v>7.02</v>
+        <v>5.99</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>[8191.71, 2966.53, 3407.99]</t>
+          <t>[2914.02, 3432.32, 4630.17]</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>[7897.55, 3133.14, 3873.69]</t>
+          <t>[2582.26, 3443.42, 4863.53]</t>
         </is>
       </c>
     </row>
@@ -4904,12 +4904,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -4923,22 +4923,22 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>306.45</v>
+        <v>63.55</v>
       </c>
       <c r="G98" t="n">
-        <v>284.44</v>
+        <v>54.68</v>
       </c>
       <c r="H98" t="n">
-        <v>7.14</v>
+        <v>1.32</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>[2951.59, 3430.25, 5694.93]</t>
+          <t>[3424.69, 4815.4, 3902.8]</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>[3133.14, 3873.69, 5466.61]</t>
+          <t>[3443.42, 4863.53, 3999.99]</t>
         </is>
       </c>
     </row>
@@ -4950,12 +4950,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -4969,22 +4969,22 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>247.41</v>
+        <v>114.27</v>
       </c>
       <c r="G99" t="n">
-        <v>201.93</v>
+        <v>102.65</v>
       </c>
       <c r="H99" t="n">
-        <v>4.79</v>
+        <v>2.42</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>[3486.67, 5646.43, 3625.3]</t>
+          <t>[4817.42, 3906.29, 4399.99]</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>[3873.69, 5466.61, 3586.35]</t>
+          <t>[4863.53, 3999.99, 4231.86]</t>
         </is>
       </c>
     </row>
@@ -4996,12 +4996,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -5011,26 +5011,26 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>(0, 1, 2, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>267.15</v>
+        <v>68.03</v>
       </c>
       <c r="G100" t="n">
-        <v>193.94</v>
+        <v>56</v>
       </c>
       <c r="H100" t="n">
-        <v>3.73</v>
+        <v>0.93</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>[5910.29, 3593.27, 4446.84]</t>
+          <t>[4045.06, 4216.76, 8127.83]</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>[5466.61, 3586.35, 4578.05]</t>
+          <t>[3999.99, 4231.86, 8235.66]</t>
         </is>
       </c>
     </row>
@@ -5042,12 +5042,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -5057,26 +5057,26 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>(0, 1, 2, 12)</t>
+          <t>(1, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>361.61</v>
+        <v>354.21</v>
       </c>
       <c r="G101" t="n">
-        <v>277.44</v>
+        <v>243.94</v>
       </c>
       <c r="H101" t="n">
-        <v>4.06</v>
+        <v>6.21</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>[3509.48, 4425.08, 8397.91]</t>
+          <t>[4316.1, 8194.38, 3147.66]</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>[3586.35, 4578.05, 9000.38]</t>
+          <t>[4231.86, 8235.66, 3753.95]</t>
         </is>
       </c>
     </row>
@@ -5088,17 +5088,17 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(1, 1, 0)</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -5107,22 +5107,22 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>96.2</v>
+        <v>104.26</v>
       </c>
       <c r="G102" t="n">
-        <v>84.98999999999999</v>
+        <v>91.06999999999999</v>
       </c>
       <c r="H102" t="n">
-        <v>4.33</v>
+        <v>2.95</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>[2352.43, 1578.46, 2348.19]</t>
+          <t>[3045.77, 5933.15, 2794.37]</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>[2230.16, 1689.58, 2326.63]</t>
+          <t>[3097.3, 5874.2, 2631.65]</t>
         </is>
       </c>
     </row>
@@ -5134,17 +5134,17 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(1, 1, 0)</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -5153,22 +5153,22 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>244.84</v>
+        <v>144.87</v>
       </c>
       <c r="G103" t="n">
-        <v>205.56</v>
+        <v>137.91</v>
       </c>
       <c r="H103" t="n">
-        <v>11.77</v>
+        <v>3.93</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>[1525.02, 2259.54, 1312.91]</t>
+          <t>[5995.46, 2830.28, 4373.93]</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>[1689.58, 2326.63, 1697.95]</t>
+          <t>[5874.2, 2631.65, 4280.1]</t>
         </is>
       </c>
     </row>
@@ -5180,17 +5180,17 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(1, 1, 0)</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -5199,22 +5199,22 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>204.9</v>
+        <v>108.58</v>
       </c>
       <c r="G104" t="n">
-        <v>185.1</v>
+        <v>93.26000000000001</v>
       </c>
       <c r="H104" t="n">
-        <v>9.699999999999999</v>
+        <v>2.7</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>[2410.43, 1399.87, 2006.16]</t>
+          <t>[2794.13, 4306.47, 7063.27]</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>[2326.63, 1697.95, 2179.57]</t>
+          <t>[2631.65, 4280.1, 6972.33]</t>
         </is>
       </c>
     </row>
@@ -5226,17 +5226,17 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(1, 1, 0)</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -5245,22 +5245,22 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>945.51</v>
+        <v>222.38</v>
       </c>
       <c r="G105" t="n">
-        <v>711.46</v>
+        <v>213.38</v>
       </c>
       <c r="H105" t="n">
-        <v>17.66</v>
+        <v>6.3</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>[1370.08, 1962.9, 5111.62]</t>
+          <t>[4148.76, 6746.79, 1967.75]</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>[1697.95, 2179.57, 6701.44]</t>
+          <t>[4280.1, 6972.33, 2251.02]</t>
         </is>
       </c>
     </row>
@@ -5272,17 +5272,17 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(1, 1, 0)</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -5291,22 +5291,22 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>495.1</v>
+        <v>167.73</v>
       </c>
       <c r="G106" t="n">
-        <v>392.07</v>
+        <v>157.38</v>
       </c>
       <c r="H106" t="n">
-        <v>9.77</v>
+        <v>6.81</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>[2244.36, 5907.45, 1872.88]</t>
+          <t>[6878.13, 2016.73, 1511.65]</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>[2179.57, 6701.44, 2190.31]</t>
+          <t>[6972.33, 2251.02, 1655.31]</t>
         </is>
       </c>
     </row>
@@ -5318,17 +5318,17 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(1, 1, 0)</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -5337,22 +5337,22 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>639.09</v>
+        <v>226.33</v>
       </c>
       <c r="G107" t="n">
-        <v>596.26</v>
+        <v>215.23</v>
       </c>
       <c r="H107" t="n">
-        <v>15.59</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>[5796.77, 1837.77, 2565.72]</t>
+          <t>[2033.39, 1526.99, 2104.49]</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>[6701.44, 2190.31, 3097.3]</t>
+          <t>[2251.02, 1655.31, 2404.24]</t>
         </is>
       </c>
     </row>
@@ -5364,12 +5364,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -5379,26 +5379,26 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>222.74</v>
+        <v>155.19</v>
       </c>
       <c r="G108" t="n">
-        <v>216.88</v>
+        <v>126.21</v>
       </c>
       <c r="H108" t="n">
-        <v>6.29</v>
+        <v>6.49</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>[2024.6, 2898.37, 5588.19]</t>
+          <t>[1637.86, 2281.6, 1554.21]</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>[2190.31, 3097.3, 5874.2]</t>
+          <t>[1655.31, 2404.24, 1792.75]</t>
         </is>
       </c>
     </row>
@@ -5410,12 +5410,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5425,26 +5425,26 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>104.26</v>
+        <v>154.97</v>
       </c>
       <c r="G109" t="n">
-        <v>91.06999999999999</v>
+        <v>143.59</v>
       </c>
       <c r="H109" t="n">
-        <v>2.95</v>
+        <v>7.16</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>[3045.77, 5933.15, 2794.37]</t>
+          <t>[2296.68, 1566.94, 2105.3]</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>[3097.3, 5874.2, 2631.65]</t>
+          <t>[2404.24, 1792.75, 2202.71]</t>
         </is>
       </c>
     </row>
@@ -5456,12 +5456,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -5471,26 +5471,26 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>144.87</v>
+        <v>305.67</v>
       </c>
       <c r="G110" t="n">
-        <v>137.91</v>
+        <v>233.3</v>
       </c>
       <c r="H110" t="n">
-        <v>3.93</v>
+        <v>6.08</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>[5995.46, 2830.28, 4373.93]</t>
+          <t>[1612.57, 2180.31, 6447.93]</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>[5874.2, 2631.65, 4280.1]</t>
+          <t>[1792.75, 2202.71, 6945.26]</t>
         </is>
       </c>
     </row>
@@ -5502,12 +5502,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5517,26 +5517,26 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>108.58</v>
+        <v>100.2</v>
       </c>
       <c r="G111" t="n">
-        <v>93.26000000000001</v>
+        <v>95.02</v>
       </c>
       <c r="H111" t="n">
-        <v>2.7</v>
+        <v>3.86</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>[2794.13, 4306.47, 7063.27]</t>
+          <t>[2324.62, 6995.62, 2238.35]</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>[2631.65, 4280.1, 6972.33]</t>
+          <t>[2202.71, 6945.26, 2125.57]</t>
         </is>
       </c>
     </row>
@@ -5548,17 +5548,17 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -5567,22 +5567,22 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>552.26</v>
+        <v>736.6799999999999</v>
       </c>
       <c r="G112" t="n">
-        <v>496.47</v>
+        <v>614.01</v>
       </c>
       <c r="H112" t="n">
-        <v>14.09</v>
+        <v>20.91</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>[2675.01, 3494.49, 2581.75]</t>
+          <t>[3265.75, 4678.89, 1884.05]</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>[2833.58, 4113.6, 3293.47]</t>
+          <t>[2421.12, 3723.42, 1925.96]</t>
         </is>
       </c>
     </row>
@@ -5594,17 +5594,17 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(1, 0, 3)</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -5613,22 +5613,22 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>560.26</v>
+        <v>560.63</v>
       </c>
       <c r="G113" t="n">
-        <v>554.9400000000001</v>
+        <v>433.85</v>
       </c>
       <c r="H113" t="n">
-        <v>15.91</v>
+        <v>16.74</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>[3568.58, 2639.66, 2719.68]</t>
+          <t>[4603.95, 1914.16, 1985.15]</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>[4113.6, 3293.47, 3185.67]</t>
+          <t>[3723.42, 1925.96, 1575.93]</t>
         </is>
       </c>
     </row>
@@ -5640,17 +5640,17 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -5659,22 +5659,22 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>365.04</v>
+        <v>287.13</v>
       </c>
       <c r="G114" t="n">
-        <v>342.46</v>
+        <v>282.12</v>
       </c>
       <c r="H114" t="n">
-        <v>10.08</v>
+        <v>14.24</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>[2784.0, 2871.59, 3935.21]</t>
+          <t>[1641.09, 1791.31, 2775.29]</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>[3293.47, 3185.67, 4139.04]</t>
+          <t>[1925.96, 1575.93, 2429.17]</t>
         </is>
       </c>
     </row>
@@ -5686,17 +5686,17 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -5705,22 +5705,22 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>2710.58</v>
+        <v>403.15</v>
       </c>
       <c r="G115" t="n">
-        <v>1626.18</v>
+        <v>397.21</v>
       </c>
       <c r="H115" t="n">
-        <v>19.65</v>
+        <v>17.75</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>[3066.98, 4206.02, 4060.04]</t>
+          <t>[1888.18, 2910.32, 3320.43]</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>[3185.67, 4139.04, 8752.92]</t>
+          <t>[1575.93, 2429.17, 2922.22]</t>
         </is>
       </c>
     </row>
@@ -5732,17 +5732,17 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -5751,22 +5751,22 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>2685.78</v>
+        <v>307.48</v>
       </c>
       <c r="G116" t="n">
-        <v>1746.85</v>
+        <v>303.19</v>
       </c>
       <c r="H116" t="n">
-        <v>27.18</v>
+        <v>10.06</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>[4268.82, 4128.31, 1416.02]</t>
+          <t>[2755.35, 3154.44, 4339.29]</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>[4139.04, 8752.92, 1902.17]</t>
+          <t>[2429.17, 2922.22, 3988.12]</t>
         </is>
       </c>
     </row>
@@ -5778,17 +5778,17 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -5797,22 +5797,22 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>2713.71</v>
+        <v>135.91</v>
       </c>
       <c r="G117" t="n">
-        <v>1726.06</v>
+        <v>129.8</v>
       </c>
       <c r="H117" t="n">
-        <v>26.63</v>
+        <v>3.8</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>[4079.47, 1400.64, 2424.32]</t>
+          <t>[3030.68, 4174.34, 3232.56]</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>[8752.92, 1902.17, 2421.12]</t>
+          <t>[2922.22, 3988.12, 3137.83]</t>
         </is>
       </c>
     </row>
@@ -5824,17 +5824,17 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -5843,22 +5843,22 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>578.9</v>
+        <v>98.54000000000001</v>
       </c>
       <c r="G118" t="n">
-        <v>515.84</v>
+        <v>92.78</v>
       </c>
       <c r="H118" t="n">
-        <v>18.38</v>
+        <v>2.63</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>[1757.18, 3102.52, 4444.56]</t>
+          <t>[4125.71, 3196.03, 3266.93]</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>[1902.17, 2421.12, 3723.42]</t>
+          <t>[3988.12, 3137.83, 3184.39]</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -5889,22 +5889,22 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>736.6799999999999</v>
+        <v>164.66</v>
       </c>
       <c r="G119" t="n">
-        <v>614.01</v>
+        <v>117.42</v>
       </c>
       <c r="H119" t="n">
-        <v>20.91</v>
+        <v>3.02</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>[3265.75, 4678.89, 1884.05]</t>
+          <t>[3161.7, 3232.72, 4408.58]</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>[2421.12, 3723.42, 1925.96]</t>
+          <t>[3137.83, 3184.39, 4128.53]</t>
         </is>
       </c>
     </row>
@@ -5916,17 +5916,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>(1, 0, 3)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -5935,22 +5935,22 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>560.63</v>
+        <v>830.85</v>
       </c>
       <c r="G120" t="n">
-        <v>433.85</v>
+        <v>574.87</v>
       </c>
       <c r="H120" t="n">
-        <v>16.74</v>
+        <v>13.7</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>[4603.95, 1914.16, 1985.15]</t>
+          <t>[3225.39, 4399.4, 5660.87]</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>[3723.42, 1925.96, 1575.93]</t>
+          <t>[3184.39, 4128.53, 4248.12]</t>
         </is>
       </c>
     </row>
@@ -5962,12 +5962,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -5981,22 +5981,22 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>287.13</v>
+        <v>816.2</v>
       </c>
       <c r="G121" t="n">
-        <v>282.12</v>
+        <v>563.79</v>
       </c>
       <c r="H121" t="n">
-        <v>14.24</v>
+        <v>13.98</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>[1641.09, 1791.31, 2775.29]</t>
+          <t>[4381.93, 5638.1, 1603.86]</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>[1925.96, 1575.93, 2429.17]</t>
+          <t>[4128.53, 4248.12, 1555.87]</t>
         </is>
       </c>
     </row>
@@ -6008,17 +6008,17 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>(1, 1, 1)</t>
+          <t>(1, 1, 2)</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -6027,22 +6027,22 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>60.84</v>
+        <v>127.69</v>
       </c>
       <c r="G122" t="n">
-        <v>49.35</v>
+        <v>122.26</v>
       </c>
       <c r="H122" t="n">
-        <v>3.98</v>
+        <v>6.89</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>[1484.73, 1076.6, 1097.87]</t>
+          <t>[1502.47, 1606.09, 1750.48]</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>[1389.65, 1031.91, 1089.57]</t>
+          <t>[1581.37, 1724.95, 1919.48]</t>
         </is>
       </c>
     </row>
@@ -6054,17 +6054,17 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>(1, 1, 1)</t>
+          <t>(1, 1, 2)</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -6073,22 +6073,22 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>47.22</v>
+        <v>122.84</v>
       </c>
       <c r="G123" t="n">
-        <v>43.85</v>
+        <v>120</v>
       </c>
       <c r="H123" t="n">
-        <v>3.71</v>
+        <v>6.52</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>[1011.9, 1039.71, 1275.25]</t>
+          <t>[1638.19, 1768.46, 1716.25]</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>[1031.91, 1089.57, 1336.93]</t>
+          <t>[1724.95, 1919.48, 1838.46]</t>
         </is>
       </c>
     </row>
@@ -6100,17 +6100,17 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>(1, 1, 1)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -6119,22 +6119,22 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>70.44</v>
+        <v>630.9</v>
       </c>
       <c r="G124" t="n">
-        <v>63.32</v>
+        <v>392.41</v>
       </c>
       <c r="H124" t="n">
-        <v>5.08</v>
+        <v>17.43</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>[1054.25, 1288.58, 1162.78]</t>
+          <t>[1854.72, 1816.61, 3375.73]</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>[1089.57, 1336.93, 1269.08]</t>
+          <t>[1919.48, 1838.46, 2285.11]</t>
         </is>
       </c>
     </row>
@@ -6146,17 +6146,17 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>(1, 1, 2)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -6165,22 +6165,22 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>34.37</v>
+        <v>672.61</v>
       </c>
       <c r="G125" t="n">
-        <v>32.34</v>
+        <v>440.21</v>
       </c>
       <c r="H125" t="n">
-        <v>2.38</v>
+        <v>20.88</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>[1352.84, 1227.31, 1433.49]</t>
+          <t>[1851.16, 3439.93, 1494.84]</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>[1336.93, 1269.08, 1472.82]</t>
+          <t>[1838.46, 2285.11, 1341.74]</t>
         </is>
       </c>
     </row>
@@ -6192,17 +6192,17 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>(1, 1, 2)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -6211,22 +6211,22 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>45.54</v>
+        <v>664.95</v>
       </c>
       <c r="G126" t="n">
-        <v>44.85</v>
+        <v>439.94</v>
       </c>
       <c r="H126" t="n">
-        <v>3.35</v>
+        <v>21.27</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>[1217.92, 1423.19, 1237.78]</t>
+          <t>[3426.96, 1489.2, 1105.84]</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>[1269.08, 1472.82, 1271.54]</t>
+          <t>[2285.11, 1341.74, 1075.34]</t>
         </is>
       </c>
     </row>
@@ -6238,41 +6238,41 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>(1, 1, 2)</t>
+          <t>(1, 1, 1)</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>50.16</v>
+        <v>160.4</v>
       </c>
       <c r="G127" t="n">
-        <v>34.62</v>
+        <v>159.66</v>
       </c>
       <c r="H127" t="n">
-        <v>2.23</v>
+        <v>13.64</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>[1459.36, 1266.83, 1495.67]</t>
+          <t>[1167.58, 908.85, 971.27]</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>[1472.82, 1271.54, 1581.37]</t>
+          <t>[1341.74, 1075.34, 1109.61]</t>
         </is>
       </c>
     </row>
@@ -6284,41 +6284,41 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>(1, 1, 2)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(1, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>82.08</v>
+        <v>104.22</v>
       </c>
       <c r="G128" t="n">
-        <v>66.38</v>
+        <v>103.25</v>
       </c>
       <c r="H128" t="n">
-        <v>4</v>
+        <v>8.58</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>[1273.77, 1503.17, 1606.25]</t>
+          <t>[975.76, 1021.65, 1307.67]</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>[1271.54, 1581.37, 1724.95]</t>
+          <t>[1075.34, 1109.61, 1429.88]</t>
         </is>
       </c>
     </row>
@@ -6330,41 +6330,41 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>(1, 1, 2)</t>
+          <t>(1, 1, 1)</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>127.69</v>
+        <v>147.98</v>
       </c>
       <c r="G129" t="n">
-        <v>122.26</v>
+        <v>120.17</v>
       </c>
       <c r="H129" t="n">
-        <v>6.89</v>
+        <v>8.43</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>[1502.47, 1606.09, 1750.48]</t>
+          <t>[1086.56, 1325.31, 1231.1]</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>[1581.37, 1724.95, 1919.48]</t>
+          <t>[1109.61, 1429.88, 1463.98]</t>
         </is>
       </c>
     </row>
@@ -6376,41 +6376,41 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>(1, 1, 2)</t>
+          <t>(1, 1, 1)</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>122.84</v>
+        <v>157.42</v>
       </c>
       <c r="G130" t="n">
-        <v>120</v>
+        <v>146.95</v>
       </c>
       <c r="H130" t="n">
-        <v>6.52</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>[1638.19, 1768.46, 1716.25]</t>
+          <t>[1338.77, 1239.72, 1452.67]</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>[1724.95, 1919.48, 1838.46]</t>
+          <t>[1429.88, 1463.98, 1578.15]</t>
         </is>
       </c>
     </row>
@@ -6422,41 +6422,41 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(1, 1, 1)</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>630.9</v>
+        <v>161.98</v>
       </c>
       <c r="G131" t="n">
-        <v>392.41</v>
+        <v>155.55</v>
       </c>
       <c r="H131" t="n">
-        <v>17.43</v>
+        <v>10.42</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>[1854.72, 1816.61, 3375.73]</t>
+          <t>[1280.17, 1486.39, 1289.98]</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>[1919.48, 1838.46, 2285.11]</t>
+          <t>[1463.98, 1578.15, 1481.05]</t>
         </is>
       </c>
     </row>
@@ -6468,17 +6468,17 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>(2, 0, 1)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -6487,22 +6487,22 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>11.08</v>
+        <v>4.97</v>
       </c>
       <c r="G132" t="n">
-        <v>10.2</v>
+        <v>3.87</v>
       </c>
       <c r="H132" t="n">
-        <v>9.27</v>
+        <v>2.7</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>[85.57, 113.14, 90.09]</t>
+          <t>[86.72, 241.19, 176.3]</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>[95.22, 128.9, 95.28]</t>
+          <t>[84.38, 242.24, 168.08]</t>
         </is>
       </c>
     </row>
@@ -6514,17 +6514,17 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>(3, 0, 3)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -6533,22 +6533,22 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>14.19</v>
+        <v>7.08</v>
       </c>
       <c r="G133" t="n">
-        <v>10.3</v>
+        <v>6.88</v>
       </c>
       <c r="H133" t="n">
-        <v>4.83</v>
+        <v>3.15</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>[134.83, 94.15, 298.11]</t>
+          <t>[237.1, 174.43, 267.23]</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>[128.9, 95.28, 274.28]</t>
+          <t>[242.24, 168.08, 258.08]</t>
         </is>
       </c>
     </row>
@@ -6560,17 +6560,17 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>(3, 0, 3)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -6579,22 +6579,22 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>86.54000000000001</v>
+        <v>9.44</v>
       </c>
       <c r="G134" t="n">
-        <v>58.09</v>
+        <v>9.31</v>
       </c>
       <c r="H134" t="n">
-        <v>28.56</v>
+        <v>3.7</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>[92.27, 297.48, 51.82]</t>
+          <t>[176.78, 269.47, 525.13]</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>[95.28, 274.28, 199.88]</t>
+          <t>[168.08, 258.08, 517.28]</t>
         </is>
       </c>
     </row>
@@ -6606,17 +6606,17 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>(2, 0, 1)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -6625,22 +6625,22 @@
         </is>
       </c>
       <c r="F135" t="n">
-        <v>85.45</v>
+        <v>3.86</v>
       </c>
       <c r="G135" t="n">
-        <v>51.66</v>
+        <v>3.62</v>
       </c>
       <c r="H135" t="n">
-        <v>25.62</v>
+        <v>2.38</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>[270.43, 51.96, 225.21]</t>
+          <t>[261.11, 514.91, 93.78]</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>[274.28, 199.88, 221.98]</t>
+          <t>[258.08, 517.28, 99.24]</t>
         </is>
       </c>
     </row>
@@ -6652,17 +6652,17 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>(2, 0, 1)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -6671,22 +6671,22 @@
         </is>
       </c>
       <c r="F136" t="n">
-        <v>85.20999999999999</v>
+        <v>5.62</v>
       </c>
       <c r="G136" t="n">
-        <v>53.1</v>
+        <v>5.59</v>
       </c>
       <c r="H136" t="n">
-        <v>27.75</v>
+        <v>3.58</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>[52.56, 226.31, 108.64]</t>
+          <t>[511.16, 93.35, 127.31]</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>[199.88, 221.98, 100.98]</t>
+          <t>[517.28, 99.24, 132.08]</t>
         </is>
       </c>
     </row>
@@ -6698,12 +6698,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -6717,22 +6717,22 @@
         </is>
       </c>
       <c r="F137" t="n">
-        <v>200.46</v>
+        <v>6.11</v>
       </c>
       <c r="G137" t="n">
-        <v>156.93</v>
+        <v>5.87</v>
       </c>
       <c r="H137" t="n">
-        <v>98.86</v>
+        <v>5.46</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>[553.48, 192.52, 132.13]</t>
+          <t>[94.04, 127.9, 94.82]</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>[221.98, 100.98, 84.38]</t>
+          <t>[99.24, 132.08, 103.05]</t>
         </is>
       </c>
     </row>
@@ -6744,12 +6744,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -6763,22 +6763,22 @@
         </is>
       </c>
       <c r="F138" t="n">
-        <v>4.46</v>
+        <v>3.86</v>
       </c>
       <c r="G138" t="n">
-        <v>4.41</v>
+        <v>2.95</v>
       </c>
       <c r="H138" t="n">
-        <v>4.03</v>
+        <v>2.35</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>[105.85, 89.31, 245.65]</t>
+          <t>[132.27, 96.83, 277.05]</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>[100.98, 84.38, 242.24]</t>
+          <t>[132.08, 103.05, 279.48]</t>
         </is>
       </c>
     </row>
@@ -6790,12 +6790,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -6809,22 +6809,22 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>4.97</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="G139" t="n">
-        <v>3.87</v>
+        <v>56.55</v>
       </c>
       <c r="H139" t="n">
-        <v>2.7</v>
+        <v>135.33</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>[86.72, 241.19, 176.3]</t>
+          <t>[96.74, 276.9, 201.07]</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>[84.38, 242.24, 168.08]</t>
+          <t>[103.05, 279.48, 40.3]</t>
         </is>
       </c>
     </row>
@@ -6836,12 +6836,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -6855,22 +6855,22 @@
         </is>
       </c>
       <c r="F140" t="n">
-        <v>7.08</v>
+        <v>95.84</v>
       </c>
       <c r="G140" t="n">
-        <v>6.88</v>
+        <v>58.2</v>
       </c>
       <c r="H140" t="n">
-        <v>3.15</v>
+        <v>138.19</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>[237.1, 174.43, 267.23]</t>
+          <t>[288.04, 206.09, 226.26]</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>[242.24, 168.08, 258.08]</t>
+          <t>[279.48, 40.3, 226.0]</t>
         </is>
       </c>
     </row>
@@ -6882,12 +6882,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -6901,22 +6901,22 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>9.44</v>
+        <v>93.52</v>
       </c>
       <c r="G141" t="n">
-        <v>9.31</v>
+        <v>55.7</v>
       </c>
       <c r="H141" t="n">
-        <v>3.7</v>
+        <v>135.24</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>[176.78, 269.47, 525.13]</t>
+          <t>[202.24, 223.61, 101.44]</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>[168.08, 258.08, 517.28]</t>
+          <t>[40.3, 226.0, 98.66]</t>
         </is>
       </c>
     </row>
@@ -6928,41 +6928,41 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>(0, 0, 1)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>4480.22</v>
+        <v>387.08</v>
       </c>
       <c r="G142" t="n">
-        <v>4000.33</v>
+        <v>237.28</v>
       </c>
       <c r="H142" t="n">
-        <v>193.37</v>
+        <v>4.52</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>[8628.28, 5227.92, 5227.92]</t>
+          <t>[3097.98, 4783.45, 3486.24]</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>[1776.37, 2576.03, 2730.73]</t>
+          <t>[3114.29, 5453.19, 3460.45]</t>
         </is>
       </c>
     </row>
@@ -6974,41 +6974,41 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>2252.54</v>
+        <v>367.97</v>
       </c>
       <c r="G143" t="n">
-        <v>2244.22</v>
+        <v>244.48</v>
       </c>
       <c r="H143" t="n">
-        <v>90.06</v>
+        <v>4.65</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>[4768.37, 4768.37, 4768.37]</t>
+          <t>[4819.8, 3512.77, 5799.56]</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>[2576.03, 2730.73, 2265.69]</t>
+          <t>[5453.19, 3460.45, 5847.3]</t>
         </is>
       </c>
     </row>
@@ -7020,41 +7020,41 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>2128.29</v>
+        <v>150.43</v>
       </c>
       <c r="G144" t="n">
-        <v>2119.73</v>
+        <v>147.37</v>
       </c>
       <c r="H144" t="n">
-        <v>85.51000000000001</v>
+        <v>2.43</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>[4630.59, 4630.59, 4630.59]</t>
+          <t>[3574.81, 6034.68, 18208.61]</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>[2730.73, 2265.69, 2536.16]</t>
+          <t>[3460.45, 5847.3, 18068.25]</t>
         </is>
       </c>
     </row>
@@ -7066,41 +7066,41 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>1851.65</v>
+        <v>431.97</v>
       </c>
       <c r="G145" t="n">
-        <v>1787.66</v>
+        <v>337.36</v>
       </c>
       <c r="H145" t="n">
-        <v>65.90000000000001</v>
+        <v>5.24</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>[4520.75, 4520.75, 4520.75]</t>
+          <t>[5751.57, 17354.36, 1797.4]</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>[2265.69, 2536.16, 5644.09]</t>
+          <t>[5847.3, 18068.25, 1999.86]</t>
         </is>
       </c>
     </row>
@@ -7112,41 +7112,41 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(2, 1, 2)</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>1379.33</v>
+        <v>3488.38</v>
       </c>
       <c r="G146" t="n">
-        <v>1315.22</v>
+        <v>3109.87</v>
       </c>
       <c r="H146" t="n">
-        <v>39.62</v>
+        <v>65.53</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>[4386.99, 4386.99, 4386.99]</t>
+          <t>[23154.25, 3217.54, 5839.14]</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>[2536.16, 5644.09, 3549.25]</t>
+          <t>[18068.25, 1999.86, 2813.21]</t>
         </is>
       </c>
     </row>
@@ -7158,41 +7158,41 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>(0, 0, 1)</t>
+          <t>(2, 1, 0)</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>722.7</v>
+        <v>169.72</v>
       </c>
       <c r="G147" t="n">
-        <v>703.22</v>
+        <v>148.61</v>
       </c>
       <c r="H147" t="n">
-        <v>17.27</v>
+        <v>5.47</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>[4717.74, 2891.72, 2588.52]</t>
+          <t>[1892.2, 2738.04, 2889.38]</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>[5644.09, 3549.25, 3114.29]</t>
+          <t>[1999.86, 2813.21, 3152.38]</t>
         </is>
       </c>
     </row>
@@ -7204,41 +7204,41 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>(2, 1, 0, 12)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>362.42</v>
+        <v>98.70999999999999</v>
       </c>
       <c r="G148" t="n">
-        <v>220.32</v>
+        <v>63.66</v>
       </c>
       <c r="H148" t="n">
-        <v>4.17</v>
+        <v>2.26</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>[3571.79, 3125.49, 4825.97]</t>
+          <t>[2983.56, 3162.74, 2624.13]</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>[3549.25, 3114.29, 5453.19]</t>
+          <t>[2813.21, 3152.38, 2634.39]</t>
         </is>
       </c>
     </row>
@@ -7250,12 +7250,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -7265,26 +7265,26 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>387.08</v>
+        <v>198.94</v>
       </c>
       <c r="G149" t="n">
-        <v>237.28</v>
+        <v>180.47</v>
       </c>
       <c r="H149" t="n">
-        <v>4.52</v>
+        <v>6.29</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>[3097.98, 4783.45, 3486.24]</t>
+          <t>[2901.16, 2407.09, 2694.44]</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>[3114.29, 5453.19, 3460.45]</t>
+          <t>[3152.38, 2634.39, 2757.33]</t>
         </is>
       </c>
     </row>
@@ -7296,41 +7296,41 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(2, 1, 0)</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>367.97</v>
+        <v>235.87</v>
       </c>
       <c r="G150" t="n">
-        <v>244.48</v>
+        <v>213.53</v>
       </c>
       <c r="H150" t="n">
-        <v>4.65</v>
+        <v>5.61</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>[4819.8, 3512.77, 5799.56]</t>
+          <t>[2707.02, 3028.12, 6668.74]</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>[5453.19, 3460.45, 5847.3]</t>
+          <t>[2634.39, 2757.33, 6965.91]</t>
         </is>
       </c>
     </row>
@@ -7342,12 +7342,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -7361,22 +7361,22 @@
         </is>
       </c>
       <c r="F151" t="n">
-        <v>150.43</v>
+        <v>1069.4</v>
       </c>
       <c r="G151" t="n">
-        <v>147.37</v>
+        <v>807.1</v>
       </c>
       <c r="H151" t="n">
-        <v>2.43</v>
+        <v>30.06</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>[3574.81, 6034.68, 18208.61]</t>
+          <t>[2911.44, 6479.25, 4074.43]</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>[3460.45, 5847.3, 18068.25]</t>
+          <t>[2757.33, 6965.91, 2293.91]</t>
         </is>
       </c>
     </row>
@@ -7388,41 +7388,41 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(0, 1, 0)</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>2685.24</v>
+        <v>7294.04</v>
       </c>
       <c r="G152" t="n">
-        <v>2668.52</v>
+        <v>6829.8</v>
       </c>
       <c r="H152" t="n">
-        <v>104.52</v>
+        <v>124.97</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>[4627.97, 4627.97, 4627.97]</t>
+          <t>[5788.3, 16109.92, 15009.05]</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>[2364.3, 1650.36, 7392.25]</t>
+          <t>[2568.13, 7223.75, 6626.0]</t>
         </is>
       </c>
     </row>
@@ -7434,41 +7434,41 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(1, 1, 0)</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>2742.2</v>
+        <v>8440.459999999999</v>
       </c>
       <c r="G153" t="n">
-        <v>2735.22</v>
+        <v>7289.83</v>
       </c>
       <c r="H153" t="n">
-        <v>111.04</v>
+        <v>105.86</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>[4475.14, 4475.14, 4475.14]</t>
+          <t>[16318.42, 8042.87, 18027.3]</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>[1650.36, 7392.25, 2011.37]</t>
+          <t>[7223.75, 6626.0, 6669.33]</t>
         </is>
       </c>
     </row>
@@ -7480,41 +7480,41 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>2394.39</v>
+        <v>1371.41</v>
       </c>
       <c r="G154" t="n">
-        <v>2304.09</v>
+        <v>1286.76</v>
       </c>
       <c r="H154" t="n">
-        <v>70.14</v>
+        <v>16.94</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>[4267.53, 4267.53, 4267.53]</t>
+          <t>[7505.41, 8621.38, 13441.97]</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>[7392.25, 2011.37, 2736.15]</t>
+          <t>[6626.0, 6669.33, 12413.16]</t>
         </is>
       </c>
     </row>
@@ -7526,41 +7526,41 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>3076.41</v>
+        <v>937.83</v>
       </c>
       <c r="G155" t="n">
-        <v>2829.51</v>
+        <v>701.66</v>
       </c>
       <c r="H155" t="n">
-        <v>76.02</v>
+        <v>10.53</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>[4375.44, 4375.44, 4375.44]</t>
+          <t>[8233.11, 12836.61, 2606.88]</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>[2011.37, 2736.15, 8860.62]</t>
+          <t>[6669.33, 12413.16, 2489.12]</t>
         </is>
       </c>
     </row>
@@ -7572,12 +7572,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -7587,26 +7587,26 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>3108.82</v>
+        <v>456.24</v>
       </c>
       <c r="G156" t="n">
-        <v>2810.35</v>
+        <v>338.61</v>
       </c>
       <c r="H156" t="n">
-        <v>75.59</v>
+        <v>6</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>[4230.06, 4230.06, 4230.06]</t>
+          <t>[11642.13, 2364.3, 1650.36]</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>[2736.15, 8860.62, 1923.47]</t>
+          <t>[12413.16, 2489.12, 1770.35]</t>
         </is>
       </c>
     </row>
@@ -7618,17 +7618,17 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>(1, 0, 0)</t>
+          <t>(0, 0, 0)</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -7637,22 +7637,22 @@
         </is>
       </c>
       <c r="F157" t="n">
-        <v>931.5</v>
+        <v>203.79</v>
       </c>
       <c r="G157" t="n">
-        <v>813.4400000000001</v>
+        <v>184.14</v>
       </c>
       <c r="H157" t="n">
-        <v>24.49</v>
+        <v>5.26</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>[10112.47, 923.21, 2756.33]</t>
+          <t>[2364.3, 1650.36, 7392.25]</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>[8860.62, 1923.47, 2568.13]</t>
+          <t>[2489.12, 1770.35, 7699.85]</t>
         </is>
       </c>
     </row>
@@ -7664,41 +7664,41 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(0, 0, 0)</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>740.04</v>
+        <v>251.84</v>
       </c>
       <c r="G158" t="n">
-        <v>658.64</v>
+        <v>237.55</v>
       </c>
       <c r="H158" t="n">
-        <v>26.51</v>
+        <v>7.73</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>[793.08, 2207.65, 6738.69]</t>
+          <t>[1650.36, 7392.25, 2011.37]</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>[1923.47, 2568.13, 7223.75]</t>
+          <t>[1770.35, 7699.85, 2296.43]</t>
         </is>
       </c>
     </row>
@@ -7710,17 +7710,17 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>(0, 1, 0)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -7729,22 +7729,22 @@
         </is>
       </c>
       <c r="F159" t="n">
-        <v>7294.04</v>
+        <v>143.54</v>
       </c>
       <c r="G159" t="n">
-        <v>6829.8</v>
+        <v>138.81</v>
       </c>
       <c r="H159" t="n">
-        <v>124.97</v>
+        <v>4.78</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>[5788.3, 16109.92, 15009.05]</t>
+          <t>[7789.36, 2119.42, 2883.14]</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>[2568.13, 7223.75, 6626.0]</t>
+          <t>[7699.85, 2296.43, 2733.24]</t>
         </is>
       </c>
     </row>
@@ -7756,17 +7756,17 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>(1, 1, 0)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -7775,22 +7775,22 @@
         </is>
       </c>
       <c r="F160" t="n">
-        <v>8440.459999999999</v>
+        <v>188.68</v>
       </c>
       <c r="G160" t="n">
-        <v>7289.83</v>
+        <v>184.81</v>
       </c>
       <c r="H160" t="n">
-        <v>105.86</v>
+        <v>5.19</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>[16318.42, 8042.87, 18027.3]</t>
+          <t>[2110.47, 2870.96, 9297.17]</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>[7223.75, 6626.0, 6669.33]</t>
+          <t>[2296.43, 2733.24, 9527.94]</t>
         </is>
       </c>
     </row>
@@ -7802,12 +7802,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -7821,22 +7821,22 @@
         </is>
       </c>
       <c r="F161" t="n">
-        <v>1371.41</v>
+        <v>446.8</v>
       </c>
       <c r="G161" t="n">
-        <v>1286.76</v>
+        <v>341.88</v>
       </c>
       <c r="H161" t="n">
-        <v>16.94</v>
+        <v>21.27</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>[7505.41, 8621.38, 13441.97]</t>
+          <t>[2960.99, 9588.72, 2081.53]</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>[6626.0, 6669.33, 12413.16]</t>
+          <t>[2733.24, 9527.94, 1344.41]</t>
         </is>
       </c>
     </row>
@@ -7848,41 +7848,41 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(0, 1, 0)</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F162" t="n">
-        <v>411.24</v>
+        <v>54.43</v>
       </c>
       <c r="G162" t="n">
-        <v>388.32</v>
+        <v>47.67</v>
       </c>
       <c r="H162" t="n">
-        <v>61.14</v>
+        <v>8.35</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>[721.21, 721.21, 721.21]</t>
+          <t>[612.84, 791.34, 589.87]</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>[1298.35, 454.7, 399.9]</t>
+          <t>[593.1, 750.95, 507.0]</t>
         </is>
       </c>
     </row>
@@ -7894,41 +7894,41 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(0, 1, 0)</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F163" t="n">
-        <v>415.46</v>
+        <v>54.73</v>
       </c>
       <c r="G163" t="n">
-        <v>398.06</v>
+        <v>49.07</v>
       </c>
       <c r="H163" t="n">
-        <v>154.36</v>
+        <v>14.05</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>[742.72, 742.72, 742.72]</t>
+          <t>[765.85, 570.87, 316.69]</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>[454.7, 399.9, 179.4]</t>
+          <t>[750.95, 507.0, 248.25]</t>
         </is>
       </c>
     </row>
@@ -7940,41 +7940,41 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F164" t="n">
-        <v>402.63</v>
+        <v>67.72</v>
       </c>
       <c r="G164" t="n">
-        <v>386.05</v>
+        <v>66.86</v>
       </c>
       <c r="H164" t="n">
-        <v>150.35</v>
+        <v>14.58</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>[725.57, 725.57, 725.57]</t>
+          <t>[562.48, 312.03, 1223.61]</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>[399.9, 179.4, 439.25]</t>
+          <t>[507.0, 248.25, 1142.3]</t>
         </is>
       </c>
     </row>
@@ -7986,41 +7986,41 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F165" t="n">
-        <v>350.62</v>
+        <v>49.1</v>
       </c>
       <c r="G165" t="n">
-        <v>311.76</v>
+        <v>43.05</v>
       </c>
       <c r="H165" t="n">
-        <v>123.7</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>[706.19, 706.19, 706.19]</t>
+          <t>[294.53, 1154.97, 1248.93]</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>[179.4, 439.25, 847.75]</t>
+          <t>[248.25, 1142.3, 1319.15]</t>
         </is>
       </c>
     </row>
@@ -8032,41 +8032,41 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F166" t="n">
-        <v>367.23</v>
+        <v>125.08</v>
       </c>
       <c r="G166" t="n">
-        <v>324.78</v>
+        <v>114.48</v>
       </c>
       <c r="H166" t="n">
-        <v>213.89</v>
+        <v>12.14</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>[665.34, 665.34, 665.34]</t>
+          <t>[1049.61, 1135.0, 397.49]</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>[439.25, 847.75, 99.5]</t>
+          <t>[1142.3, 1319.15, 464.08]</t>
         </is>
       </c>
     </row>
@@ -8078,17 +8078,17 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>(1, 0, 0)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -8097,22 +8097,22 @@
         </is>
       </c>
       <c r="F167" t="n">
-        <v>210.18</v>
+        <v>174.68</v>
       </c>
       <c r="G167" t="n">
-        <v>184.36</v>
+        <v>167.31</v>
       </c>
       <c r="H167" t="n">
-        <v>38.78</v>
+        <v>26.71</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>[604.64, 57.18, 325.46]</t>
+          <t>[1555.53, 582.64, 548.04]</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>[847.75, 99.5, 593.1]</t>
+          <t>[1319.15, 464.08, 401.05]</t>
         </is>
       </c>
     </row>
@@ -8124,17 +8124,17 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>(0, 1, 0)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -8143,22 +8143,22 @@
         </is>
       </c>
       <c r="F168" t="n">
-        <v>7.07</v>
+        <v>74.38</v>
       </c>
       <c r="G168" t="n">
-        <v>5.56</v>
+        <v>72.61</v>
       </c>
       <c r="H168" t="n">
-        <v>2.33</v>
+        <v>23.25</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>[94.48, 581.94, 751.44]</t>
+          <t>[529.57, 496.01, 236.97]</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>[99.5, 593.1, 750.95]</t>
+          <t>[464.08, 401.05, 179.6]</t>
         </is>
       </c>
     </row>
@@ -8170,17 +8170,17 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>(0, 1, 0)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -8189,22 +8189,22 @@
         </is>
       </c>
       <c r="F169" t="n">
-        <v>54.43</v>
+        <v>90.16</v>
       </c>
       <c r="G169" t="n">
-        <v>47.67</v>
+        <v>81.22</v>
       </c>
       <c r="H169" t="n">
-        <v>8.35</v>
+        <v>23.57</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>[612.84, 791.34, 589.87]</t>
+          <t>[466.93, 222.45, 578.38]</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>[593.1, 750.95, 507.0]</t>
+          <t>[401.05, 179.6, 443.45]</t>
         </is>
       </c>
     </row>
@@ -8216,17 +8216,17 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>(0, 1, 0)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -8235,22 +8235,22 @@
         </is>
       </c>
       <c r="F170" t="n">
-        <v>54.73</v>
+        <v>153.75</v>
       </c>
       <c r="G170" t="n">
-        <v>49.07</v>
+        <v>123.66</v>
       </c>
       <c r="H170" t="n">
-        <v>14.05</v>
+        <v>22.09</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>[765.85, 570.87, 316.69]</t>
+          <t>[208.0, 539.15, 1101.59]</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>[750.95, 507.0, 248.25]</t>
+          <t>[179.6, 443.45, 854.7]</t>
         </is>
       </c>
     </row>
@@ -8262,12 +8262,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -8281,22 +8281,22 @@
         </is>
       </c>
       <c r="F171" t="n">
-        <v>67.72</v>
+        <v>107.67</v>
       </c>
       <c r="G171" t="n">
-        <v>66.86</v>
+        <v>86.78</v>
       </c>
       <c r="H171" t="n">
-        <v>14.58</v>
+        <v>19.32</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>[562.48, 312.03, 1223.61]</t>
+          <t>[505.09, 1029.02, 127.49]</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>[507.0, 248.25, 1142.3]</t>
+          <t>[443.45, 854.7, 103.1]</t>
         </is>
       </c>
     </row>
@@ -8308,41 +8308,41 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>(2, 1, 1, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>706.5</v>
+        <v>331.22</v>
       </c>
       <c r="G172" t="n">
-        <v>618.96</v>
+        <v>317.08</v>
       </c>
       <c r="H172" t="n">
-        <v>22.83</v>
+        <v>7.62</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>[2732.66, 3302.86, 3823.56]</t>
+          <t>[3633.52, 4343.47, 4891.23]</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>[2459.35, 2801.67, 2741.18]</t>
+          <t>[4061.35, 4014.27, 4697.04]</t>
         </is>
       </c>
     </row>
@@ -8354,17 +8354,17 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -8373,22 +8373,22 @@
         </is>
       </c>
       <c r="F173" t="n">
-        <v>624.14</v>
+        <v>709.46</v>
       </c>
       <c r="G173" t="n">
-        <v>511.14</v>
+        <v>645.53</v>
       </c>
       <c r="H173" t="n">
-        <v>18.45</v>
+        <v>12.91</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>[3312.26, 3691.26, 3020.77]</t>
+          <t>[4597.67, 5017.21, 6979.32]</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>[2801.67, 2741.18, 2948.03]</t>
+          <t>[4014.27, 4697.04, 5946.29]</t>
         </is>
       </c>
     </row>
@@ -8400,17 +8400,17 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -8419,22 +8419,22 @@
         </is>
       </c>
       <c r="F174" t="n">
-        <v>435.63</v>
+        <v>737.78</v>
       </c>
       <c r="G174" t="n">
-        <v>283.69</v>
+        <v>615.2</v>
       </c>
       <c r="H174" t="n">
-        <v>10.23</v>
+        <v>9.27</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>[3492.35, 2891.92, 3184.25]</t>
+          <t>[4740.37, 6788.28, 8498.81]</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>[2741.18, 2948.03, 3140.46]</t>
+          <t>[4697.04, 5946.29, 7538.52]</t>
         </is>
       </c>
     </row>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -8465,22 +8465,22 @@
         </is>
       </c>
       <c r="F175" t="n">
-        <v>531.84</v>
+        <v>722.23</v>
       </c>
       <c r="G175" t="n">
-        <v>421.07</v>
+        <v>623.6900000000001</v>
       </c>
       <c r="H175" t="n">
-        <v>10.74</v>
+        <v>10.27</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>[2620.15, 3062.43, 3752.08]</t>
+          <t>[6760.64, 8481.21, 2592.93]</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>[2948.03, 3140.46, 4609.38]</t>
+          <t>[5946.29, 7538.52, 2478.9]</t>
         </is>
       </c>
     </row>
@@ -8492,41 +8492,41 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>(1, 0, 0)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(0, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>880.3099999999999</v>
+        <v>612.1900000000001</v>
       </c>
       <c r="G176" t="n">
-        <v>723.72</v>
+        <v>552.42</v>
       </c>
       <c r="H176" t="n">
-        <v>14.76</v>
+        <v>15.95</v>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>[3230.62, 3844.08, 3990.91]</t>
+          <t>[8258.41, 2658.81, 3196.93]</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>[3140.46, 4609.38, 5306.59]</t>
+          <t>[7538.52, 2478.9, 2439.47]</t>
         </is>
       </c>
     </row>
@@ -8538,12 +8538,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -8557,22 +8557,22 @@
         </is>
       </c>
       <c r="F177" t="n">
-        <v>1035.78</v>
+        <v>397.87</v>
       </c>
       <c r="G177" t="n">
-        <v>1009.17</v>
+        <v>355.85</v>
       </c>
       <c r="H177" t="n">
-        <v>21.48</v>
+        <v>13.79</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>[3797.28, 3969.8, 3182.72]</t>
+          <t>[2351.49, 3001.05, 3242.75]</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>[4609.38, 5306.59, 4061.35]</t>
+          <t>[2478.9, 2439.47, 2864.2]</t>
         </is>
       </c>
     </row>
@@ -8584,41 +8584,41 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>(1, 0, 0)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(0, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F178" t="n">
-        <v>728.1900000000001</v>
+        <v>476.91</v>
       </c>
       <c r="G178" t="n">
-        <v>631.84</v>
+        <v>435.55</v>
       </c>
       <c r="H178" t="n">
-        <v>13.66</v>
+        <v>16.5</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>[4314.66, 3294.44, 4150.96]</t>
+          <t>[3082.78, 3351.58, 3048.63]</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>[5306.59, 4061.35, 4014.27]</t>
+          <t>[2439.47, 2864.2, 2872.67]</t>
         </is>
       </c>
     </row>
@@ -8630,12 +8630,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -8649,22 +8649,22 @@
         </is>
       </c>
       <c r="F179" t="n">
-        <v>331.22</v>
+        <v>256.53</v>
       </c>
       <c r="G179" t="n">
-        <v>317.08</v>
+        <v>188.84</v>
       </c>
       <c r="H179" t="n">
-        <v>7.62</v>
+        <v>6.88</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>[3633.52, 4343.47, 4891.23]</t>
+          <t>[2948.87, 2824.3, 3140.28]</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>[4061.35, 4014.27, 4697.04]</t>
+          <t>[2864.2, 2872.67, 2706.78]</t>
         </is>
       </c>
     </row>
@@ -8676,41 +8676,41 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>(1, 0, 0)</t>
+          <t>(0, 0, 1)</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(0, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F180" t="n">
-        <v>709.46</v>
+        <v>359.4</v>
       </c>
       <c r="G180" t="n">
-        <v>645.53</v>
+        <v>260.81</v>
       </c>
       <c r="H180" t="n">
-        <v>12.91</v>
+        <v>9.23</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>[4597.67, 5017.21, 6979.32]</t>
+          <t>[2967.79, 3317.14, 4297.2]</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>[4014.27, 4697.04, 5946.29]</t>
+          <t>[2872.67, 2706.78, 4220.25]</t>
         </is>
       </c>
     </row>
@@ -8722,12 +8722,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -8741,22 +8741,22 @@
         </is>
       </c>
       <c r="F181" t="n">
-        <v>737.78</v>
+        <v>340.37</v>
       </c>
       <c r="G181" t="n">
-        <v>615.2</v>
+        <v>311.2</v>
       </c>
       <c r="H181" t="n">
-        <v>9.27</v>
+        <v>9.06</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>[4740.37, 6788.28, 8498.81]</t>
+          <t>[3162.45, 4094.67, 4428.43]</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>[4697.04, 5946.29, 7538.52]</t>
+          <t>[2706.78, 4220.25, 4780.77]</t>
         </is>
       </c>
     </row>
@@ -8768,12 +8768,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -8787,22 +8787,22 @@
         </is>
       </c>
       <c r="F182" t="n">
-        <v>485.89</v>
+        <v>163.55</v>
       </c>
       <c r="G182" t="n">
-        <v>446.46</v>
+        <v>153.77</v>
       </c>
       <c r="H182" t="n">
-        <v>19</v>
+        <v>4.43</v>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>[3721.04, 1933.27, 1279.46]</t>
+          <t>[3558.35, 5312.83, 2215.34]</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>[3942.12, 2622.99, 1708.04]</t>
+          <t>[3472.15, 5090.14, 2367.75]</t>
         </is>
       </c>
     </row>
@@ -8814,12 +8814,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -8833,22 +8833,22 @@
         </is>
       </c>
       <c r="F183" t="n">
-        <v>454.84</v>
+        <v>144.09</v>
       </c>
       <c r="G183" t="n">
-        <v>417.95</v>
+        <v>127.34</v>
       </c>
       <c r="H183" t="n">
-        <v>20.06</v>
+        <v>4.1</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>[1977.12, 1307.43, 1506.98]</t>
+          <t>[5269.96, 2197.7, 2009.52]</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>[2622.99, 1708.04, 1714.33]</t>
+          <t>[5090.14, 2367.75, 2041.65]</t>
         </is>
       </c>
     </row>
@@ -8860,12 +8860,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -8879,22 +8879,22 @@
         </is>
       </c>
       <c r="F184" t="n">
-        <v>161.05</v>
+        <v>121.46</v>
       </c>
       <c r="G184" t="n">
-        <v>124.89</v>
+        <v>102.62</v>
       </c>
       <c r="H184" t="n">
-        <v>7.2</v>
+        <v>4.15</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>[1439.35, 1661.9, 1854.2]</t>
+          <t>[2173.3, 1987.36, 3713.03]</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>[1708.04, 1714.33, 1907.73]</t>
+          <t>[2367.75, 2041.65, 3772.16]</t>
         </is>
       </c>
     </row>
@@ -8906,12 +8906,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -8925,22 +8925,22 @@
         </is>
       </c>
       <c r="F185" t="n">
-        <v>118.13</v>
+        <v>184.9</v>
       </c>
       <c r="G185" t="n">
-        <v>100.83</v>
+        <v>121.16</v>
       </c>
       <c r="H185" t="n">
-        <v>6.43</v>
+        <v>3.06</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>[1768.03, 1968.78, 1260.22]</t>
+          <t>[2043.03, 3817.19, 3690.7]</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>[1714.33, 1907.73, 1447.97]</t>
+          <t>[2041.65, 3772.16, 4007.77]</t>
         </is>
       </c>
     </row>
@@ -8952,12 +8952,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -8971,22 +8971,22 @@
         </is>
       </c>
       <c r="F186" t="n">
-        <v>120.08</v>
+        <v>188.21</v>
       </c>
       <c r="G186" t="n">
-        <v>91</v>
+        <v>139.85</v>
       </c>
       <c r="H186" t="n">
-        <v>5.79</v>
+        <v>3.86</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>[1947.27, 1246.26, 2377.48]</t>
+          <t>[3816.17, 3689.97, 2277.44]</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>[1907.73, 1447.97, 2345.72]</t>
+          <t>[3772.16, 4007.77, 2335.19]</t>
         </is>
       </c>
     </row>
@@ -8998,12 +8998,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -9017,22 +9017,22 @@
         </is>
       </c>
       <c r="F187" t="n">
-        <v>122.69</v>
+        <v>388.26</v>
       </c>
       <c r="G187" t="n">
-        <v>84.48</v>
+        <v>326.45</v>
       </c>
       <c r="H187" t="n">
-        <v>5.33</v>
+        <v>13.1</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>[1237.84, 2361.72, 3444.85]</t>
+          <t>[3676.62, 2268.48, 1482.79]</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>[1447.97, 2345.72, 3472.15]</t>
+          <t>[4007.77, 2335.19, 2064.27]</t>
         </is>
       </c>
     </row>
@@ -9044,12 +9044,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -9063,22 +9063,22 @@
         </is>
       </c>
       <c r="F188" t="n">
-        <v>229.65</v>
+        <v>313.15</v>
       </c>
       <c r="G188" t="n">
-        <v>212.93</v>
+        <v>192.14</v>
       </c>
       <c r="H188" t="n">
-        <v>5.78</v>
+        <v>9.42</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>[2490.29, 3632.11, 5424.39]</t>
+          <t>[2329.51, 1522.7, 1596.81]</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>[2345.72, 3472.15, 5090.14]</t>
+          <t>[2335.19, 2064.27, 1625.97]</t>
         </is>
       </c>
     </row>
@@ -9090,12 +9090,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -9109,22 +9109,22 @@
         </is>
       </c>
       <c r="F189" t="n">
-        <v>163.55</v>
+        <v>315.09</v>
       </c>
       <c r="G189" t="n">
-        <v>153.77</v>
+        <v>213.11</v>
       </c>
       <c r="H189" t="n">
-        <v>4.43</v>
+        <v>10.58</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>[3558.35, 5312.83, 2215.34]</t>
+          <t>[1523.89, 1598.06, 1778.35]</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>[3472.15, 5090.14, 2367.75]</t>
+          <t>[2064.27, 1625.97, 1849.39]</t>
         </is>
       </c>
     </row>
@@ -9136,12 +9136,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -9155,22 +9155,22 @@
         </is>
       </c>
       <c r="F190" t="n">
-        <v>144.09</v>
+        <v>104.44</v>
       </c>
       <c r="G190" t="n">
-        <v>127.34</v>
+        <v>86.81999999999999</v>
       </c>
       <c r="H190" t="n">
-        <v>4.1</v>
+        <v>5.07</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>[5269.96, 2197.7, 2009.52]</t>
+          <t>[1764.48, 1965.61, 1421.92]</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>[5090.14, 2367.75, 2041.65]</t>
+          <t>[1625.97, 1849.39, 1416.17]</t>
         </is>
       </c>
     </row>
@@ -9182,12 +9182,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -9201,22 +9201,22 @@
         </is>
       </c>
       <c r="F191" t="n">
-        <v>121.46</v>
+        <v>41.37</v>
       </c>
       <c r="G191" t="n">
-        <v>102.62</v>
+        <v>37.15</v>
       </c>
       <c r="H191" t="n">
-        <v>4.15</v>
+        <v>2.13</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>[2173.3, 1987.36, 3713.03]</t>
+          <t>[1910.33, 1382.35, 2340.84]</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>[2367.75, 2041.65, 3772.16]</t>
+          <t>[1849.39, 1416.17, 2324.16]</t>
         </is>
       </c>
     </row>
@@ -9228,41 +9228,41 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(0, 0, 0)</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F192" t="n">
-        <v>3726.89</v>
+        <v>2735.27</v>
       </c>
       <c r="G192" t="n">
-        <v>3046.99</v>
+        <v>1989.05</v>
       </c>
       <c r="H192" t="n">
-        <v>33.59</v>
+        <v>14.6</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>[4952.08, 4942.73, 5388.08]</t>
+          <t>[10634.39, 11173.69, 10707.65]</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>[6351.97, 11020.91, 7050.97]</t>
+          <t>[9372.79, 15738.07, 10566.5]</t>
         </is>
       </c>
     </row>
@@ -9274,41 +9274,41 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(0, 0, 0)</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F193" t="n">
-        <v>3546.05</v>
+        <v>2702.99</v>
       </c>
       <c r="G193" t="n">
-        <v>2954.38</v>
+        <v>1798.24</v>
       </c>
       <c r="H193" t="n">
-        <v>30.02</v>
+        <v>12.09</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>[5327.66, 5844.3, 7260.8]</t>
+          <t>[11086.6, 10883.37, 11015.59]</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>[11020.91, 7050.97, 9224.01]</t>
+          <t>[15738.07, 10566.5, 11441.98]</t>
         </is>
       </c>
     </row>
@@ -9320,41 +9320,41 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>(0, 1, 2)</t>
+          <t>(0, 0, 0)</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F194" t="n">
-        <v>1338.81</v>
+        <v>7877.07</v>
       </c>
       <c r="G194" t="n">
-        <v>1174.26</v>
+        <v>4769.7</v>
       </c>
       <c r="H194" t="n">
-        <v>15.69</v>
+        <v>17.47</v>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>[9099.48, 8269.93, 7296.36]</t>
+          <t>[10600.43, 10794.9, 15725.15]</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>[7050.97, 9224.01, 6776.16]</t>
+          <t>[10566.5, 11441.98, 29353.24]</t>
         </is>
       </c>
     </row>
@@ -9366,41 +9366,41 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>(0, 1, 2)</t>
+          <t>(0, 0, 0)</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F195" t="n">
-        <v>5738.29</v>
+        <v>7926.25</v>
       </c>
       <c r="G195" t="n">
-        <v>3883.58</v>
+        <v>5277.56</v>
       </c>
       <c r="H195" t="n">
-        <v>27.77</v>
+        <v>23.52</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>[7604.46, 7003.83, 5912.02]</t>
+          <t>[10806.9, 15729.93, 6892.86]</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>[9224.01, 6776.16, 15715.54]</t>
+          <t>[11441.98, 29353.24, 8467.16]</t>
         </is>
       </c>
     </row>
@@ -9412,17 +9412,17 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>(0, 1, 2)</t>
+          <t>(0, 0, 0)</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -9431,22 +9431,22 @@
         </is>
       </c>
       <c r="F196" t="n">
-        <v>5572.61</v>
+        <v>7921.19</v>
       </c>
       <c r="G196" t="n">
-        <v>3598.1</v>
+        <v>5351.13</v>
       </c>
       <c r="H196" t="n">
-        <v>26.14</v>
+        <v>25.29</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>[7495.21, 6101.36, 6487.78]</t>
+          <t>[15750.43, 6928.43, 8944.19]</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>[6776.16, 15715.54, 6948.86]</t>
+          <t>[29353.24, 8467.16, 8032.34]</t>
         </is>
       </c>
     </row>
@@ -9458,17 +9458,17 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>(0, 1, 2)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -9477,22 +9477,22 @@
         </is>
       </c>
       <c r="F197" t="n">
-        <v>5706.81</v>
+        <v>1447.32</v>
       </c>
       <c r="G197" t="n">
-        <v>3686.53</v>
+        <v>1071.21</v>
       </c>
       <c r="H197" t="n">
-        <v>25.91</v>
+        <v>13.17</v>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>[5868.41, 6375.49, 10011.88]</t>
+          <t>[7692.32, 10415.78, 8280.36]</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>[15715.54, 6948.86, 9372.79]</t>
+          <t>[8467.16, 8032.34, 8225.02]</t>
         </is>
       </c>
     </row>
@@ -9504,17 +9504,17 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>(1, 0, 0)</t>
+          <t>(2, 0, 2)</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -9523,22 +9523,22 @@
         </is>
       </c>
       <c r="F198" t="n">
-        <v>2955.49</v>
+        <v>2135.61</v>
       </c>
       <c r="G198" t="n">
-        <v>2748.27</v>
+        <v>1795.83</v>
       </c>
       <c r="H198" t="n">
-        <v>25.56</v>
+        <v>25</v>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>[8881.75, 11399.94, 11453.29]</t>
+          <t>[10129.44, 7971.11, 9664.77]</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>[6948.86, 9372.79, 15738.07]</t>
+          <t>[8032.34, 8225.02, 6628.3]</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -9569,22 +9569,22 @@
         </is>
       </c>
       <c r="F199" t="n">
-        <v>2735.27</v>
+        <v>1322.41</v>
       </c>
       <c r="G199" t="n">
-        <v>1989.05</v>
+        <v>920.53</v>
       </c>
       <c r="H199" t="n">
-        <v>14.6</v>
+        <v>13.43</v>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>[10634.39, 11173.69, 10707.65]</t>
+          <t>[7861.03, 8885.31, 7557.0]</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>[9372.79, 15738.07, 10566.5]</t>
+          <t>[8225.02, 6628.3, 7697.58]</t>
         </is>
       </c>
     </row>
@@ -9596,12 +9596,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -9615,22 +9615,22 @@
         </is>
       </c>
       <c r="F200" t="n">
-        <v>2702.99</v>
+        <v>1383.32</v>
       </c>
       <c r="G200" t="n">
-        <v>1798.24</v>
+        <v>1064.74</v>
       </c>
       <c r="H200" t="n">
-        <v>12.09</v>
+        <v>14.82</v>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>[11086.6, 10883.37, 11015.59]</t>
+          <t>[8870.85, 7581.47, 10002.93]</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>[15738.07, 10566.5, 11441.98]</t>
+          <t>[6628.3, 7697.58, 9167.36]</t>
         </is>
       </c>
     </row>
@@ -9642,12 +9642,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -9661,22 +9661,22 @@
         </is>
       </c>
       <c r="F201" t="n">
-        <v>7877.07</v>
+        <v>856.71</v>
       </c>
       <c r="G201" t="n">
-        <v>4769.7</v>
+        <v>701.8200000000001</v>
       </c>
       <c r="H201" t="n">
-        <v>17.47</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>[10600.43, 10794.9, 15725.15]</t>
+          <t>[7618.92, 9914.57, 7300.7]</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>[10566.5, 11441.98, 29353.24]</t>
+          <t>[7697.58, 9167.36, 8580.29]</t>
         </is>
       </c>
     </row>
